--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q337"/>
+  <dimension ref="A1:Q336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,14 +715,10 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -796,14 +792,10 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -877,14 +869,10 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -958,14 +946,10 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1039,14 +1023,10 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1120,14 +1100,10 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1201,14 +1177,10 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1282,14 +1254,10 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1363,14 +1331,10 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1444,14 +1408,10 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1525,14 +1485,10 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1606,14 +1562,10 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1687,14 +1639,10 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1768,14 +1716,10 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1849,14 +1793,10 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1930,14 +1870,10 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2011,14 +1947,10 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2092,14 +2024,10 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2173,14 +2101,10 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2254,14 +2178,10 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2335,14 +2255,10 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2416,14 +2332,10 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2497,14 +2409,10 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2578,14 +2486,10 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2659,14 +2563,10 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2740,14 +2640,10 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2821,14 +2717,10 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2902,14 +2794,10 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2983,14 +2871,10 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3064,14 +2948,10 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3137,7 +3017,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n"/>
+      <c r="N37" s="6" t="n">
+        <v>58.9830508474576</v>
+      </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3145,14 +3027,10 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3218,7 +3096,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N38" s="4" t="n"/>
+      <c r="N38" s="6" t="n">
+        <v>58.6571056062582</v>
+      </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3226,14 +3106,10 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3299,7 +3175,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n"/>
+      <c r="N39" s="6" t="n">
+        <v>58.3311603650587</v>
+      </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3307,14 +3185,10 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3380,7 +3254,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n"/>
+      <c r="N40" s="6" t="n">
+        <v>58.0052151238592</v>
+      </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3388,14 +3264,10 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3461,7 +3333,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N41" s="4" t="n"/>
+      <c r="N41" s="6" t="n">
+        <v>57.6792698826597</v>
+      </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3469,14 +3343,10 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3542,7 +3412,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n"/>
+      <c r="N42" s="6" t="n">
+        <v>57.3533246414602</v>
+      </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3550,14 +3422,10 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q42" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3623,7 +3491,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n"/>
+      <c r="N43" s="6" t="n">
+        <v>57.0273794002608</v>
+      </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3631,14 +3501,10 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3704,7 +3570,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n"/>
+      <c r="N44" s="6" t="n">
+        <v>56.7014341590613</v>
+      </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3712,14 +3580,10 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3785,7 +3649,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n"/>
+      <c r="N45" s="6" t="n">
+        <v>56.3754889178618</v>
+      </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3793,14 +3659,10 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q45" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -3866,7 +3728,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n"/>
+      <c r="N46" s="6" t="n">
+        <v>56.0495436766623</v>
+      </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3874,14 +3738,10 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3947,7 +3807,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n"/>
+      <c r="N47" s="6" t="n">
+        <v>55.7235984354628</v>
+      </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3955,14 +3817,10 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -4028,7 +3886,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n"/>
+      <c r="N48" s="6" t="n">
+        <v>55.53698769911</v>
+      </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4036,14 +3896,10 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -4109,7 +3965,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n"/>
+      <c r="N49" s="6" t="n">
+        <v>55.3503769627572</v>
+      </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4117,14 +3975,10 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q49" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4190,7 +4044,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n"/>
+      <c r="N50" s="6" t="n">
+        <v>55.1637662264044</v>
+      </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4198,14 +4054,10 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4271,7 +4123,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n"/>
+      <c r="N51" s="6" t="n">
+        <v>54.9771554900516</v>
+      </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4279,14 +4133,10 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q51" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4352,7 +4202,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n"/>
+      <c r="N52" s="6" t="n">
+        <v>54.7905447536988</v>
+      </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4360,14 +4212,10 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4433,7 +4281,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n"/>
+      <c r="N53" s="6" t="n">
+        <v>54.603934017346</v>
+      </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4441,14 +4291,10 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4514,7 +4360,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n"/>
+      <c r="N54" s="6" t="n">
+        <v>54.4173232809931</v>
+      </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4522,14 +4370,10 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4595,7 +4439,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n"/>
+      <c r="N55" s="6" t="n">
+        <v>54.2307125446403</v>
+      </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4603,14 +4449,10 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -4676,7 +4518,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n"/>
+      <c r="N56" s="6" t="n">
+        <v>54.0441018082875</v>
+      </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4684,14 +4528,10 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4757,7 +4597,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n"/>
+      <c r="N57" s="6" t="n">
+        <v>53.8574910719347</v>
+      </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4765,14 +4607,10 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -4838,7 +4676,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n"/>
+      <c r="N58" s="6" t="n">
+        <v>53.6711070800975</v>
+      </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4846,14 +4686,10 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4919,7 +4755,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n"/>
+      <c r="N59" s="6" t="n">
+        <v>53.4847230882603</v>
+      </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4927,14 +4765,10 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -5000,7 +4834,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n"/>
+      <c r="N60" s="6" t="n">
+        <v>53.2983390964231</v>
+      </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5008,14 +4844,10 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -5081,7 +4913,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n"/>
+      <c r="N61" s="6" t="n">
+        <v>53.1119551045859</v>
+      </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5089,14 +4923,10 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q61" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -5162,7 +4992,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n"/>
+      <c r="N62" s="6" t="n">
+        <v>52.9255711127487</v>
+      </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5170,14 +5002,10 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q62" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -5243,7 +5071,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n"/>
+      <c r="N63" s="6" t="n">
+        <v>52.7671447196871</v>
+      </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5251,14 +5081,10 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q63" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -5324,7 +5150,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n"/>
+      <c r="N64" s="6" t="n">
+        <v>52.6366759254011</v>
+      </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5332,14 +5160,10 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q64" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5405,7 +5229,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N65" s="4" t="n"/>
+      <c r="N65" s="6" t="n">
+        <v>52.5341647298906</v>
+      </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5413,14 +5239,10 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q65" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -5486,7 +5308,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n"/>
+      <c r="N66" s="6" t="n">
+        <v>52.4596111331557</v>
+      </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5494,14 +5318,10 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q66" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -5567,7 +5387,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N67" s="4" t="n"/>
+      <c r="N67" s="6" t="n">
+        <v>52.4130151351964</v>
+      </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5575,14 +5397,10 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q67" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -5648,7 +5466,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n"/>
+      <c r="N68" s="6" t="n">
+        <v>52.3477807380534</v>
+      </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5656,14 +5476,10 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q68" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5729,7 +5545,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n"/>
+      <c r="N69" s="6" t="n">
+        <v>52.2949719403662</v>
+      </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5737,14 +5555,10 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q69" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -5810,7 +5624,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n"/>
+      <c r="N70" s="6" t="n">
+        <v>52.2338793719177</v>
+      </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5818,14 +5634,10 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q70" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5899,14 +5711,10 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q71" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -5980,14 +5788,10 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -6021,7 +5825,7 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>2026</v>
+        <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -6035,22 +5839,22 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Bosques</t>
+          <t>Electricidad</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>bosques</t>
+          <t>electricidad</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>AG.LND.FRST.ZS</t>
+          <t>EG.ELC.ACCS.ZS</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>Superficie forestal como porcentaje del territorio</t>
+          <t>Acceso a electricidad</t>
         </is>
       </c>
       <c r="N73" s="4" t="n"/>
@@ -6061,14 +5865,10 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -6102,7 +5902,7 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
@@ -6142,7 +5942,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6179,7 +5979,7 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -6219,7 +6019,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6256,7 +6056,7 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -6296,7 +6096,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6333,7 +6133,7 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -6373,7 +6173,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6410,7 +6210,7 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -6450,7 +6250,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6487,7 +6287,7 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -6527,7 +6327,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6564,7 +6364,7 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -6604,7 +6404,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6641,7 +6441,7 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -6681,7 +6481,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6718,7 +6518,7 @@
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
@@ -6758,7 +6558,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6795,7 +6595,7 @@
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -6835,7 +6635,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6872,7 +6672,7 @@
         </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -6912,7 +6712,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6949,7 +6749,7 @@
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -6989,7 +6789,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -7026,7 +6826,7 @@
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
@@ -7066,7 +6866,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7103,7 +6903,7 @@
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -7143,7 +6943,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7180,7 +6980,7 @@
         </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -7220,7 +7020,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7257,7 +7057,7 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -7297,7 +7097,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7334,7 +7134,7 @@
         </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
@@ -7374,7 +7174,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7411,7 +7211,7 @@
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -7451,7 +7251,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7488,7 +7288,7 @@
         </is>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -7528,7 +7328,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7565,7 +7365,7 @@
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -7605,7 +7405,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7642,7 +7442,7 @@
         </is>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
@@ -7682,7 +7482,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7719,7 +7519,7 @@
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -7759,7 +7559,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7796,7 +7596,7 @@
         </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
@@ -7836,7 +7636,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7873,7 +7673,7 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -7913,7 +7713,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7950,7 +7750,7 @@
         </is>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
@@ -7990,7 +7790,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -8027,7 +7827,7 @@
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -8067,7 +7867,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8104,7 +7904,7 @@
         </is>
       </c>
       <c r="G100" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
@@ -8144,7 +7944,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8181,7 +7981,7 @@
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -8221,7 +8021,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8258,7 +8058,7 @@
         </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
@@ -8298,7 +8098,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8335,7 +8135,7 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -8375,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8412,7 +8212,7 @@
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
@@ -8452,7 +8252,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8489,7 +8289,7 @@
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -8521,7 +8321,9 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N105" s="4" t="n"/>
+      <c r="N105" s="6" t="n">
+        <v>97.82020300000001</v>
+      </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8529,7 +8331,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8566,7 +8368,7 @@
         </is>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
@@ -8599,7 +8401,7 @@
         </is>
       </c>
       <c r="N106" s="6" t="n">
-        <v>97.82020300000001</v>
+        <v>98.2395324707031</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
@@ -8608,7 +8410,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8645,7 +8447,7 @@
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -8678,7 +8480,7 @@
         </is>
       </c>
       <c r="N107" s="6" t="n">
-        <v>98.2395324707031</v>
+        <v>98.3233337402344</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
@@ -8687,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8724,7 +8526,7 @@
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
@@ -8756,8 +8558,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N108" s="6" t="n">
-        <v>98.3233337402344</v>
+      <c r="N108" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
@@ -8766,7 +8568,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8803,7 +8605,7 @@
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -8835,8 +8637,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N109" s="5" t="n">
-        <v>99</v>
+      <c r="N109" s="6" t="n">
+        <v>98.484130859375</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
@@ -8845,7 +8647,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8882,7 +8684,7 @@
         </is>
       </c>
       <c r="G110" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
@@ -8915,7 +8717,7 @@
         </is>
       </c>
       <c r="N110" s="6" t="n">
-        <v>98.484130859375</v>
+        <v>98.7</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
@@ -8924,7 +8726,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8961,7 +8763,7 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -8994,7 +8796,7 @@
         </is>
       </c>
       <c r="N111" s="6" t="n">
-        <v>98.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
@@ -9003,7 +8805,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9040,7 +8842,7 @@
         </is>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
@@ -9073,7 +8875,7 @@
         </is>
       </c>
       <c r="N112" s="6" t="n">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
@@ -9082,7 +8884,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9119,7 +8921,7 @@
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -9161,7 +8963,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9198,7 +9000,7 @@
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
@@ -9231,7 +9033,7 @@
         </is>
       </c>
       <c r="N114" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
@@ -9240,7 +9042,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9277,7 +9079,7 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -9310,7 +9112,7 @@
         </is>
       </c>
       <c r="N115" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
@@ -9319,7 +9121,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9356,7 +9158,7 @@
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -9389,7 +9191,7 @@
         </is>
       </c>
       <c r="N116" s="6" t="n">
-        <v>99.8</v>
+        <v>95.7</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
@@ -9398,7 +9200,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9435,7 +9237,7 @@
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -9468,7 +9270,7 @@
         </is>
       </c>
       <c r="N117" s="6" t="n">
-        <v>95.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
@@ -9477,7 +9279,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9514,7 +9316,7 @@
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
@@ -9547,7 +9349,7 @@
         </is>
       </c>
       <c r="N118" s="6" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
@@ -9556,7 +9358,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9593,7 +9395,7 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -9626,7 +9428,7 @@
         </is>
       </c>
       <c r="N119" s="6" t="n">
-        <v>98.8</v>
+        <v>99.3</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
@@ -9635,7 +9437,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9672,7 +9474,7 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
@@ -9705,7 +9507,7 @@
         </is>
       </c>
       <c r="N120" s="6" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
@@ -9714,7 +9516,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9751,7 +9553,7 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -9793,7 +9595,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9830,7 +9632,7 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
@@ -9862,8 +9664,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N122" s="6" t="n">
-        <v>98.90000000000001</v>
+      <c r="N122" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
@@ -9872,7 +9674,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9909,7 +9711,7 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -9941,8 +9743,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N123" s="5" t="n">
-        <v>99</v>
+      <c r="N123" s="6" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
@@ -9951,7 +9753,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9988,7 +9790,7 @@
         </is>
       </c>
       <c r="G124" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
@@ -10021,7 +9823,7 @@
         </is>
       </c>
       <c r="N124" s="6" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
@@ -10030,7 +9832,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10067,7 +9869,7 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -10100,7 +9902,7 @@
         </is>
       </c>
       <c r="N125" s="6" t="n">
-        <v>98.8</v>
+        <v>99.3</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
@@ -10109,7 +9911,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10146,7 +9948,7 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
@@ -10179,7 +9981,7 @@
         </is>
       </c>
       <c r="N126" s="6" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
@@ -10188,7 +9990,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10225,7 +10027,7 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -10257,8 +10059,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N127" s="6" t="n">
-        <v>99.40000000000001</v>
+      <c r="N127" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
@@ -10267,7 +10069,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10304,7 +10106,7 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
@@ -10346,7 +10148,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10383,7 +10185,7 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -10415,8 +10217,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N129" s="5" t="n">
-        <v>100</v>
+      <c r="N129" s="6" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
@@ -10425,7 +10227,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10462,7 +10264,7 @@
         </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
@@ -10495,7 +10297,7 @@
         </is>
       </c>
       <c r="N130" s="6" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
@@ -10504,7 +10306,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10541,7 +10343,7 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -10574,7 +10376,7 @@
         </is>
       </c>
       <c r="N131" s="6" t="n">
-        <v>99.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
@@ -10583,7 +10385,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10620,7 +10422,7 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
@@ -10653,7 +10455,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
@@ -10662,7 +10464,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10699,7 +10501,7 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -10732,7 +10534,7 @@
         </is>
       </c>
       <c r="N133" s="6" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
@@ -10741,7 +10543,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10778,7 +10580,7 @@
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
@@ -10810,8 +10612,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N134" s="6" t="n">
-        <v>99.90000000000001</v>
+      <c r="N134" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
@@ -10820,7 +10622,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10857,7 +10659,7 @@
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -10899,7 +10701,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10936,7 +10738,7 @@
         </is>
       </c>
       <c r="G136" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
@@ -10978,7 +10780,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -11015,7 +10817,7 @@
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -11057,7 +10859,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11094,7 +10896,7 @@
         </is>
       </c>
       <c r="G138" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
@@ -11126,9 +10928,7 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N138" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="N138" s="4" t="n"/>
       <c r="O138" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11136,7 +10936,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11173,7 +10973,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -11197,12 +10997,12 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.ACCS.ZS</t>
+          <t>EG.ELC.RNEW.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Acceso a electricidad</t>
+          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11213,7 +11013,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11250,7 +11050,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11290,7 +11090,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11327,7 +11127,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11367,7 +11167,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11404,7 +11204,7 @@
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11444,7 +11244,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11481,7 +11281,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11521,7 +11321,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11558,7 +11358,7 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11598,7 +11398,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11635,7 +11435,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11675,7 +11475,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11712,7 +11512,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11752,7 +11552,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11789,7 +11589,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11829,7 +11629,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11866,7 +11666,7 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11906,7 +11706,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11943,7 +11743,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11983,7 +11783,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -12020,7 +11820,7 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -12060,7 +11860,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12097,7 +11897,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -12137,7 +11937,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12174,7 +11974,7 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12214,7 +12014,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12251,7 +12051,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12291,7 +12091,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12328,7 +12128,7 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12368,7 +12168,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12405,7 +12205,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12445,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12482,7 +12282,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12522,7 +12322,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12559,7 +12359,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12599,7 +12399,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12636,7 +12436,7 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12676,7 +12476,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12713,7 +12513,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12753,7 +12553,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12790,7 +12590,7 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12830,7 +12630,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12867,7 +12667,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12907,7 +12707,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12944,7 +12744,7 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -12984,7 +12784,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13021,7 +12821,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -13061,7 +12861,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13098,7 +12898,7 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -13138,7 +12938,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13175,7 +12975,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13215,7 +13015,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13252,7 +13052,7 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13292,7 +13092,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13329,7 +13129,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13369,7 +13169,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13406,7 +13206,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13446,7 +13246,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13483,7 +13283,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13515,7 +13315,9 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N169" s="4" t="n"/>
+      <c r="N169" s="6" t="n">
+        <v>62.3438579929536</v>
+      </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13523,7 +13325,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13560,7 +13362,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13593,7 +13395,7 @@
         </is>
       </c>
       <c r="N170" s="6" t="n">
-        <v>62.3438579929536</v>
+        <v>70.3254022135561</v>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
@@ -13602,7 +13404,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13639,7 +13441,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13672,7 +13474,7 @@
         </is>
       </c>
       <c r="N171" s="6" t="n">
-        <v>70.3254022135561</v>
+        <v>70.09341637010679</v>
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
@@ -13681,7 +13483,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13718,7 +13520,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13751,7 +13553,7 @@
         </is>
       </c>
       <c r="N172" s="6" t="n">
-        <v>70.09341637010679</v>
+        <v>68.42985212302899</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
@@ -13760,7 +13562,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13797,7 +13599,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13830,7 +13632,7 @@
         </is>
       </c>
       <c r="N173" s="6" t="n">
-        <v>68.42985212302899</v>
+        <v>72.0068519116553</v>
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
@@ -13839,7 +13641,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13876,7 +13678,7 @@
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13909,7 +13711,7 @@
         </is>
       </c>
       <c r="N174" s="6" t="n">
-        <v>72.0068519116553</v>
+        <v>70.0514663834654</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
@@ -13918,7 +13720,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13955,7 +13757,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -13988,7 +13790,7 @@
         </is>
       </c>
       <c r="N175" s="6" t="n">
-        <v>70.0514663834654</v>
+        <v>71.237498015558</v>
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
@@ -13997,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14034,7 +13836,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -14067,7 +13869,7 @@
         </is>
       </c>
       <c r="N176" s="6" t="n">
-        <v>71.237498015558</v>
+        <v>73.359380003843</v>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
@@ -14076,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14113,7 +13915,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -14146,7 +13948,7 @@
         </is>
       </c>
       <c r="N177" s="6" t="n">
-        <v>73.359380003843</v>
+        <v>71.59649946849279</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
@@ -14155,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14192,7 +13994,7 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14225,7 +14027,7 @@
         </is>
       </c>
       <c r="N178" s="6" t="n">
-        <v>71.59649946849279</v>
+        <v>75.1646552472619</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -14234,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14271,7 +14073,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14304,7 +14106,7 @@
         </is>
       </c>
       <c r="N179" s="6" t="n">
-        <v>75.1646552472619</v>
+        <v>73.7484021531353</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
@@ -14313,7 +14115,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14350,7 +14152,7 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14383,7 +14185,7 @@
         </is>
       </c>
       <c r="N180" s="6" t="n">
-        <v>73.7484021531353</v>
+        <v>67.0679878826884</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
@@ -14392,7 +14194,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14429,7 +14231,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14462,7 +14264,7 @@
         </is>
       </c>
       <c r="N181" s="6" t="n">
-        <v>67.0679878826884</v>
+        <v>64.8151373949397</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
@@ -14471,7 +14273,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14508,7 +14310,7 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14541,7 +14343,7 @@
         </is>
       </c>
       <c r="N182" s="6" t="n">
-        <v>64.8151373949397</v>
+        <v>65.83572609414431</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
@@ -14550,7 +14352,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14587,7 +14389,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14620,7 +14422,7 @@
         </is>
       </c>
       <c r="N183" s="6" t="n">
-        <v>65.83572609414431</v>
+        <v>70.94119195375541</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
@@ -14629,7 +14431,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14666,7 +14468,7 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14699,7 +14501,7 @@
         </is>
       </c>
       <c r="N184" s="6" t="n">
-        <v>70.94119195375541</v>
+        <v>73.28606809382831</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -14708,7 +14510,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14745,7 +14547,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14778,7 +14580,7 @@
         </is>
       </c>
       <c r="N185" s="6" t="n">
-        <v>73.28606809382831</v>
+        <v>73.9008893155349</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
@@ -14787,7 +14589,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14824,7 +14626,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14857,7 +14659,7 @@
         </is>
       </c>
       <c r="N186" s="6" t="n">
-        <v>73.9008893155349</v>
+        <v>72.7246397114189</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
@@ -14866,7 +14668,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14903,7 +14705,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14936,7 +14738,7 @@
         </is>
       </c>
       <c r="N187" s="6" t="n">
-        <v>72.7246397114189</v>
+        <v>72.7965497875051</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
@@ -14945,7 +14747,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14982,7 +14784,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -15015,7 +14817,7 @@
         </is>
       </c>
       <c r="N188" s="6" t="n">
-        <v>72.7965497875051</v>
+        <v>71.6609231333517</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -15024,7 +14826,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15061,7 +14863,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -15094,7 +14896,7 @@
         </is>
       </c>
       <c r="N189" s="6" t="n">
-        <v>71.6609231333517</v>
+        <v>67.242625937084</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
@@ -15103,7 +14905,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15140,7 +14942,7 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -15173,7 +14975,7 @@
         </is>
       </c>
       <c r="N190" s="6" t="n">
-        <v>67.242625937084</v>
+        <v>70.7004672541846</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
@@ -15182,7 +14984,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15219,7 +15021,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15252,7 +15054,7 @@
         </is>
       </c>
       <c r="N191" s="6" t="n">
-        <v>70.7004672541846</v>
+        <v>67.0600784236679</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15298,7 +15100,7 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15331,7 +15133,7 @@
         </is>
       </c>
       <c r="N192" s="6" t="n">
-        <v>67.0600784236679</v>
+        <v>65.96440553278519</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
@@ -15340,7 +15142,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15377,7 +15179,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15410,7 +15212,7 @@
         </is>
       </c>
       <c r="N193" s="6" t="n">
-        <v>65.96440553278519</v>
+        <v>77.5369122989602</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
@@ -15419,7 +15221,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15456,7 +15258,7 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15489,7 +15291,7 @@
         </is>
       </c>
       <c r="N194" s="6" t="n">
-        <v>77.5369122989602</v>
+        <v>65.53966478494149</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
@@ -15498,7 +15300,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15535,7 +15337,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15568,7 +15370,7 @@
         </is>
       </c>
       <c r="N195" s="6" t="n">
-        <v>65.53966478494149</v>
+        <v>62.32403609516</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
@@ -15577,7 +15379,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15614,7 +15416,7 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15647,7 +15449,7 @@
         </is>
       </c>
       <c r="N196" s="6" t="n">
-        <v>62.32403609516</v>
+        <v>51.4746640846626</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -15656,7 +15458,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15693,7 +15495,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15726,7 +15528,7 @@
         </is>
       </c>
       <c r="N197" s="6" t="n">
-        <v>51.4746640846626</v>
+        <v>63.2932794208759</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
@@ -15735,7 +15537,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15772,7 +15574,7 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15805,7 +15607,7 @@
         </is>
       </c>
       <c r="N198" s="6" t="n">
-        <v>63.2932794208759</v>
+        <v>65.9218035546249</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
@@ -15814,7 +15616,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15653,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15884,7 +15686,7 @@
         </is>
       </c>
       <c r="N199" s="6" t="n">
-        <v>65.9218035546249</v>
+        <v>84.45121523562889</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
         <is>
@@ -15893,7 +15695,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15930,7 +15732,7 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15963,7 +15765,7 @@
         </is>
       </c>
       <c r="N200" s="6" t="n">
-        <v>84.45121523562889</v>
+        <v>81.72207575243419</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
@@ -15972,7 +15774,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16009,7 +15811,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -16041,9 +15843,7 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N201" s="6" t="n">
-        <v>81.72207575243419</v>
-      </c>
+      <c r="N201" s="4" t="n"/>
       <c r="O201" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16051,7 +15851,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16088,7 +15888,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -16128,7 +15928,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16165,7 +15965,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16205,7 +16005,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16242,7 +16042,7 @@
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16282,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16319,7 +16119,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16333,22 +16133,22 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>electricidad</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.RNEW.ZS</t>
+          <t>EG.USE.PCAP.KG.OE</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
+          <t>Uso de energía per cápita</t>
         </is>
       </c>
       <c r="N205" s="4" t="n"/>
@@ -16359,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16396,7 +16196,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16436,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16473,7 +16273,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16513,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16550,7 +16350,7 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16590,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16627,7 +16427,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16667,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16704,7 +16504,7 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16744,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16781,7 +16581,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16821,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16858,7 +16658,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16898,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16935,7 +16735,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16975,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17012,7 +16812,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -17052,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17089,7 +16889,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -17129,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17166,7 +16966,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17206,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17243,7 +17043,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17283,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17320,7 +17120,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17360,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17397,7 +17197,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17437,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17474,7 +17274,7 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17514,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17551,7 +17351,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17591,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17628,7 +17428,7 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17668,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17705,7 +17505,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17745,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17782,7 +17582,7 @@
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17822,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17859,7 +17659,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17899,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17936,7 +17736,7 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17976,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18013,7 +17813,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -18053,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18090,7 +17890,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -18130,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18167,7 +17967,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18207,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18244,7 +18044,7 @@
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18284,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18321,7 +18121,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18361,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18398,7 +18198,7 @@
         </is>
       </c>
       <c r="G232" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18438,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18475,7 +18275,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18515,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18552,7 +18352,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18592,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18629,7 +18429,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18661,7 +18461,9 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N235" s="4" t="n"/>
+      <c r="N235" s="6" t="n">
+        <v>1997.56479057799</v>
+      </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18669,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18706,7 +18508,7 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18739,7 +18541,7 @@
         </is>
       </c>
       <c r="N236" s="6" t="n">
-        <v>1997.56479057799</v>
+        <v>2037.30182520885</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -18748,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18785,7 +18587,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18818,7 +18620,7 @@
         </is>
       </c>
       <c r="N237" s="6" t="n">
-        <v>2037.30182520885</v>
+        <v>2226.55481105961</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
@@ -18827,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18864,7 +18666,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18897,7 +18699,7 @@
         </is>
       </c>
       <c r="N238" s="6" t="n">
-        <v>2226.55481105961</v>
+        <v>2027.59967205093</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -18906,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18943,7 +18745,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18976,7 +18778,7 @@
         </is>
       </c>
       <c r="N239" s="6" t="n">
-        <v>2027.59967205093</v>
+        <v>2299.11785137022</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
@@ -18985,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19022,7 +18824,7 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -19055,7 +18857,7 @@
         </is>
       </c>
       <c r="N240" s="6" t="n">
-        <v>2299.11785137022</v>
+        <v>2111.33770063193</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -19064,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19101,7 +18903,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -19134,7 +18936,7 @@
         </is>
       </c>
       <c r="N241" s="6" t="n">
-        <v>2111.33770063193</v>
+        <v>2203.62644762536</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
@@ -19143,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19180,7 +18982,7 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19213,7 +19015,7 @@
         </is>
       </c>
       <c r="N242" s="6" t="n">
-        <v>2203.62644762536</v>
+        <v>2149.90770739915</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -19222,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19259,7 +19061,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19292,7 +19094,7 @@
         </is>
       </c>
       <c r="N243" s="6" t="n">
-        <v>2149.90770739915</v>
+        <v>2218.43187719732</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
@@ -19301,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19338,7 +19140,7 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19371,7 +19173,7 @@
         </is>
       </c>
       <c r="N244" s="6" t="n">
-        <v>2218.43187719732</v>
+        <v>2399.16210710328</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19380,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19417,7 +19219,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19450,7 +19252,7 @@
         </is>
       </c>
       <c r="N245" s="6" t="n">
-        <v>2399.16210710328</v>
+        <v>2391.36796026802</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
@@ -19459,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19496,7 +19298,7 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19529,7 +19331,7 @@
         </is>
       </c>
       <c r="N246" s="6" t="n">
-        <v>2391.36796026802</v>
+        <v>2188.40606705914</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -19538,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19575,7 +19377,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19608,7 +19410,7 @@
         </is>
       </c>
       <c r="N247" s="6" t="n">
-        <v>2188.40606705914</v>
+        <v>2648.88652521803</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19617,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19654,7 +19456,7 @@
         </is>
       </c>
       <c r="G248" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19687,7 +19489,7 @@
         </is>
       </c>
       <c r="N248" s="6" t="n">
-        <v>2648.88652521803</v>
+        <v>2432.12630470112</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19696,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19733,7 +19535,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19766,7 +19568,7 @@
         </is>
       </c>
       <c r="N249" s="6" t="n">
-        <v>2432.12630470112</v>
+        <v>2305.02805179379</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19775,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19812,7 +19614,7 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19845,7 +19647,7 @@
         </is>
       </c>
       <c r="N250" s="6" t="n">
-        <v>2305.02805179379</v>
+        <v>2371.58340737061</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19854,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19891,7 +19693,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19924,7 +19726,7 @@
         </is>
       </c>
       <c r="N251" s="6" t="n">
-        <v>2371.58340737061</v>
+        <v>2377.64028480756</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19933,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19970,7 +19772,7 @@
         </is>
       </c>
       <c r="G252" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -20003,7 +19805,7 @@
         </is>
       </c>
       <c r="N252" s="6" t="n">
-        <v>2377.64028480756</v>
+        <v>2391.33788149518</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -20012,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20049,7 +19851,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -20082,7 +19884,7 @@
         </is>
       </c>
       <c r="N253" s="6" t="n">
-        <v>2391.33788149518</v>
+        <v>2346.01163837283</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
@@ -20091,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20128,7 +19930,7 @@
         </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -20161,7 +19963,7 @@
         </is>
       </c>
       <c r="N254" s="6" t="n">
-        <v>2346.01163837283</v>
+        <v>2231.75458660546</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -20170,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20207,7 +20009,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20240,7 +20042,7 @@
         </is>
       </c>
       <c r="N255" s="6" t="n">
-        <v>2231.75458660546</v>
+        <v>2621.20702328211</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
@@ -20249,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20286,7 +20088,7 @@
         </is>
       </c>
       <c r="G256" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20319,7 +20121,7 @@
         </is>
       </c>
       <c r="N256" s="6" t="n">
-        <v>2621.20702328211</v>
+        <v>2309.9066118944</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
@@ -20328,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20365,7 +20167,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20398,7 +20200,7 @@
         </is>
       </c>
       <c r="N257" s="6" t="n">
-        <v>2309.9066118944</v>
+        <v>2310.75269478151</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20407,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20444,7 +20246,7 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20477,7 +20279,7 @@
         </is>
       </c>
       <c r="N258" s="6" t="n">
-        <v>2310.75269478151</v>
+        <v>2529.2097489945</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
@@ -20486,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20523,7 +20325,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20556,7 +20358,7 @@
         </is>
       </c>
       <c r="N259" s="6" t="n">
-        <v>2529.2097489945</v>
+        <v>2173.57093050952</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20565,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20602,7 +20404,7 @@
         </is>
       </c>
       <c r="G260" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20635,7 +20437,7 @@
         </is>
       </c>
       <c r="N260" s="6" t="n">
-        <v>2173.57093050952</v>
+        <v>2098.46944015591</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
@@ -20644,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20681,7 +20483,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20714,7 +20516,7 @@
         </is>
       </c>
       <c r="N261" s="6" t="n">
-        <v>2098.46944015591</v>
+        <v>2009.0681450604</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
@@ -20723,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20760,7 +20562,7 @@
         </is>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20793,7 +20595,7 @@
         </is>
       </c>
       <c r="N262" s="6" t="n">
-        <v>2009.0681450604</v>
+        <v>1933.19114696252</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
@@ -20802,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20839,7 +20641,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20872,7 +20674,7 @@
         </is>
       </c>
       <c r="N263" s="6" t="n">
-        <v>1933.19114696252</v>
+        <v>1451.3949056587</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
@@ -20881,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20918,7 +20720,7 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20951,7 +20753,7 @@
         </is>
       </c>
       <c r="N264" s="6" t="n">
-        <v>1451.3949056587</v>
+        <v>1379.73439965</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
@@ -20960,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20997,7 +20799,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -21030,7 +20832,7 @@
         </is>
       </c>
       <c r="N265" s="6" t="n">
-        <v>1379.73439965</v>
+        <v>1093.43160664363</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
@@ -21039,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21076,7 +20878,7 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -21109,7 +20911,7 @@
         </is>
       </c>
       <c r="N266" s="6" t="n">
-        <v>1093.43160664363</v>
+        <v>1409.82623845927</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
@@ -21118,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21155,7 +20957,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -21188,7 +20990,7 @@
         </is>
       </c>
       <c r="N267" s="6" t="n">
-        <v>1409.82623845927</v>
+        <v>1364.68351163595</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
@@ -21197,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21234,7 +21036,7 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21267,7 +21069,7 @@
         </is>
       </c>
       <c r="N268" s="6" t="n">
-        <v>1364.68351163595</v>
+        <v>1331.23284099658</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
@@ -21276,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21313,7 +21115,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21345,9 +21147,7 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N269" s="6" t="n">
-        <v>1331.23284099658</v>
-      </c>
+      <c r="N269" s="4" t="n"/>
       <c r="O269" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21355,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21392,7 +21192,7 @@
         </is>
       </c>
       <c r="G270" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21432,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21469,7 +21269,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21483,22 +21283,22 @@
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Recursos naturales</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>recursos_naturales</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>EG.USE.PCAP.KG.OE</t>
+          <t>NY.GDP.TOTL.RT.ZS</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Uso de energía per cápita</t>
+          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N271" s="4" t="n"/>
@@ -21509,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21546,7 +21346,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21586,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21623,7 +21423,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21663,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21700,7 +21500,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21740,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21777,7 +21577,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21817,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21854,7 +21654,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21894,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21931,7 +21731,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21971,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22008,7 +21808,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -22048,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22085,7 +21885,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -22125,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22162,7 +21962,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22202,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22239,7 +22039,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22271,7 +22071,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N281" s="4" t="n"/>
+      <c r="N281" s="6" t="n">
+        <v>5.48772130601331</v>
+      </c>
       <c r="O281" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22279,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22316,7 +22118,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22349,7 +22151,7 @@
         </is>
       </c>
       <c r="N282" s="6" t="n">
-        <v>5.48772130601331</v>
+        <v>7.38794104909662</v>
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
@@ -22358,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22395,7 +22197,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22428,7 +22230,7 @@
         </is>
       </c>
       <c r="N283" s="6" t="n">
-        <v>7.38794104909662</v>
+        <v>7.19271915747182</v>
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
@@ -22437,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22474,7 +22276,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22507,7 +22309,7 @@
         </is>
       </c>
       <c r="N284" s="6" t="n">
-        <v>7.19271915747182</v>
+        <v>10.7554427076038</v>
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
@@ -22516,7 +22318,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22553,7 +22355,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22586,7 +22388,7 @@
         </is>
       </c>
       <c r="N285" s="6" t="n">
-        <v>10.7554427076038</v>
+        <v>33.9478841729493</v>
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
@@ -22595,7 +22397,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22632,7 +22434,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22665,7 +22467,7 @@
         </is>
       </c>
       <c r="N286" s="6" t="n">
-        <v>33.9478841729493</v>
+        <v>24.8915014056924</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
@@ -22674,7 +22476,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22711,7 +22513,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22744,7 +22546,7 @@
         </is>
       </c>
       <c r="N287" s="6" t="n">
-        <v>24.8915014056924</v>
+        <v>22.9931513860828</v>
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
@@ -22753,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22790,7 +22592,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22823,7 +22625,7 @@
         </is>
       </c>
       <c r="N288" s="6" t="n">
-        <v>22.9931513860828</v>
+        <v>16.1985343555775</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
@@ -22832,7 +22634,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22869,7 +22671,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22902,7 +22704,7 @@
         </is>
       </c>
       <c r="N289" s="6" t="n">
-        <v>16.1985343555775</v>
+        <v>15.8263995123574</v>
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
@@ -22911,7 +22713,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22948,7 +22750,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22981,7 +22783,7 @@
         </is>
       </c>
       <c r="N290" s="6" t="n">
-        <v>15.8263995123574</v>
+        <v>36.481380981255</v>
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
@@ -22990,7 +22792,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23027,7 +22829,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -23060,7 +22862,7 @@
         </is>
       </c>
       <c r="N291" s="6" t="n">
-        <v>36.481380981255</v>
+        <v>34.4312946645093</v>
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
@@ -23069,7 +22871,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23106,7 +22908,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -23139,7 +22941,7 @@
         </is>
       </c>
       <c r="N292" s="6" t="n">
-        <v>34.4312946645093</v>
+        <v>24.750858904318</v>
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
@@ -23148,7 +22950,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23185,7 +22987,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23218,7 +23020,7 @@
         </is>
       </c>
       <c r="N293" s="6" t="n">
-        <v>24.750858904318</v>
+        <v>13.1086608763643</v>
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
@@ -23227,7 +23029,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23264,7 +23066,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23297,7 +23099,7 @@
         </is>
       </c>
       <c r="N294" s="6" t="n">
-        <v>13.1086608763643</v>
+        <v>17.0995109701258</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
@@ -23306,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23343,7 +23145,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23376,7 +23178,7 @@
         </is>
       </c>
       <c r="N295" s="6" t="n">
-        <v>17.0995109701258</v>
+        <v>19.0260300794035</v>
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
@@ -23385,7 +23187,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23422,7 +23224,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23455,7 +23257,7 @@
         </is>
       </c>
       <c r="N296" s="6" t="n">
-        <v>19.0260300794035</v>
+        <v>16.3107385078032</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
@@ -23464,7 +23266,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23501,7 +23303,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23534,7 +23336,7 @@
         </is>
       </c>
       <c r="N297" s="6" t="n">
-        <v>16.3107385078032</v>
+        <v>8.00102414924425</v>
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
@@ -23543,7 +23345,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23580,7 +23382,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23613,7 +23415,7 @@
         </is>
       </c>
       <c r="N298" s="6" t="n">
-        <v>8.00102414924425</v>
+        <v>15.9166311155573</v>
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
@@ -23622,7 +23424,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23659,7 +23461,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23692,7 +23494,7 @@
         </is>
       </c>
       <c r="N299" s="6" t="n">
-        <v>15.9166311155573</v>
+        <v>10.0130859589153</v>
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
@@ -23701,7 +23503,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23738,7 +23540,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23771,7 +23573,7 @@
         </is>
       </c>
       <c r="N300" s="6" t="n">
-        <v>10.0130859589153</v>
+        <v>20.9626504331607</v>
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
@@ -23780,7 +23582,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23817,7 +23619,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23850,7 +23652,7 @@
         </is>
       </c>
       <c r="N301" s="6" t="n">
-        <v>20.9626504331607</v>
+        <v>29.2548511239111</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
@@ -23859,7 +23661,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23896,7 +23698,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23929,7 +23731,7 @@
         </is>
       </c>
       <c r="N302" s="6" t="n">
-        <v>29.2548511239111</v>
+        <v>16.6639894189064</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
@@ -23938,7 +23740,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23975,7 +23777,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -24008,7 +23810,7 @@
         </is>
       </c>
       <c r="N303" s="6" t="n">
-        <v>16.6639894189064</v>
+        <v>15.7571776112482</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
@@ -24017,7 +23819,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24054,7 +23856,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -24087,7 +23889,7 @@
         </is>
       </c>
       <c r="N304" s="6" t="n">
-        <v>15.7571776112482</v>
+        <v>15.7932181812518</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
@@ -24096,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24133,7 +23935,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -24166,7 +23968,7 @@
         </is>
       </c>
       <c r="N305" s="6" t="n">
-        <v>15.7932181812518</v>
+        <v>16.2198265911409</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
@@ -24175,7 +23977,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24212,7 +24014,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24245,7 +24047,7 @@
         </is>
       </c>
       <c r="N306" s="6" t="n">
-        <v>16.2198265911409</v>
+        <v>15.1363210095652</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
@@ -24254,7 +24056,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24291,7 +24093,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24324,7 +24126,7 @@
         </is>
       </c>
       <c r="N307" s="6" t="n">
-        <v>15.1363210095652</v>
+        <v>23.8367720643582</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
@@ -24333,7 +24135,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24370,7 +24172,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24403,7 +24205,7 @@
         </is>
       </c>
       <c r="N308" s="6" t="n">
-        <v>23.8367720643582</v>
+        <v>18.0963540802062</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
@@ -24412,7 +24214,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24449,7 +24251,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24482,7 +24284,7 @@
         </is>
       </c>
       <c r="N309" s="6" t="n">
-        <v>18.0963540802062</v>
+        <v>9.06347009522954</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24491,7 +24293,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24528,7 +24330,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24561,7 +24363,7 @@
         </is>
       </c>
       <c r="N310" s="6" t="n">
-        <v>9.06347009522954</v>
+        <v>13.269532614572</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24570,7 +24372,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24607,7 +24409,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24640,7 +24442,7 @@
         </is>
       </c>
       <c r="N311" s="6" t="n">
-        <v>13.269532614572</v>
+        <v>20.5761295010598</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24649,7 +24451,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24686,7 +24488,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24719,7 +24521,7 @@
         </is>
       </c>
       <c r="N312" s="6" t="n">
-        <v>20.5761295010598</v>
+        <v>15.3442903568827</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24728,7 +24530,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24765,7 +24567,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24798,7 +24600,7 @@
         </is>
       </c>
       <c r="N313" s="6" t="n">
-        <v>15.3442903568827</v>
+        <v>19.4545884689745</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24807,7 +24609,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24844,7 +24646,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24877,7 +24679,7 @@
         </is>
       </c>
       <c r="N314" s="6" t="n">
-        <v>19.4545884689745</v>
+        <v>21.8955843439596</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24886,7 +24688,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24923,7 +24725,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24956,7 +24758,7 @@
         </is>
       </c>
       <c r="N315" s="6" t="n">
-        <v>21.8955843439596</v>
+        <v>23.8297115705399</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24965,7 +24767,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25002,7 +24804,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -25035,7 +24837,7 @@
         </is>
       </c>
       <c r="N316" s="6" t="n">
-        <v>23.8297115705399</v>
+        <v>29.2230041014033</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -25044,7 +24846,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25081,7 +24883,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -25114,7 +24916,7 @@
         </is>
       </c>
       <c r="N317" s="6" t="n">
-        <v>29.2230041014033</v>
+        <v>28.0774680117788</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -25123,7 +24925,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25160,7 +24962,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -25193,7 +24995,7 @@
         </is>
       </c>
       <c r="N318" s="6" t="n">
-        <v>28.0774680117788</v>
+        <v>23.1186941835454</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -25202,7 +25004,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25239,7 +25041,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25272,7 +25074,7 @@
         </is>
       </c>
       <c r="N319" s="6" t="n">
-        <v>23.1186941835454</v>
+        <v>23.9223070628002</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25281,7 +25083,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25318,7 +25120,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25351,7 +25153,7 @@
         </is>
       </c>
       <c r="N320" s="6" t="n">
-        <v>23.9223070628002</v>
+        <v>10.5416668243022</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25360,7 +25162,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25397,7 +25199,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25430,7 +25232,7 @@
         </is>
       </c>
       <c r="N321" s="6" t="n">
-        <v>10.5416668243022</v>
+        <v>12.380878328857</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25439,7 +25241,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25476,7 +25278,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25509,7 +25311,7 @@
         </is>
       </c>
       <c r="N322" s="6" t="n">
-        <v>12.380878328857</v>
+        <v>24.4753357613612</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25518,7 +25320,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25555,7 +25357,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25588,7 +25390,7 @@
         </is>
       </c>
       <c r="N323" s="6" t="n">
-        <v>24.4753357613612</v>
+        <v>18.7812359044725</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25597,7 +25399,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25634,7 +25436,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25667,7 +25469,7 @@
         </is>
       </c>
       <c r="N324" s="6" t="n">
-        <v>18.7812359044725</v>
+        <v>17.6253449138361</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25676,7 +25478,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25713,7 +25515,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25746,7 +25548,7 @@
         </is>
       </c>
       <c r="N325" s="6" t="n">
-        <v>17.6253449138361</v>
+        <v>11.8465082797294</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25755,7 +25557,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25792,7 +25594,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25824,9 +25626,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N326" s="6" t="n">
-        <v>11.8465082797294</v>
-      </c>
+      <c r="N326" s="4" t="n"/>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25834,7 +25634,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25871,7 +25671,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25911,7 +25711,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25948,7 +25748,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25988,7 +25788,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26025,7 +25825,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -26065,7 +25865,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26102,7 +25902,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -26142,7 +25942,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26179,7 +25979,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26219,7 +26019,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26256,7 +26056,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26296,7 +26096,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26333,7 +26133,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26373,7 +26173,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26410,7 +26210,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26450,7 +26250,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26487,7 +26287,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26527,7 +26327,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26564,7 +26364,7 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26604,87 +26404,10 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>Energía y ambiente</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>energia_y_ambiente</t>
-        </is>
-      </c>
-      <c r="J337" s="4" t="inlineStr">
-        <is>
-          <t>Recursos naturales</t>
-        </is>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>recursos_naturales</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
-        </is>
-      </c>
-      <c r="M337" s="4" t="inlineStr">
-        <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
-        </is>
-      </c>
-      <c r="N337" s="4" t="n"/>
-      <c r="O337" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P337" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26766,7 +26489,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -26787,7 +26510,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12399,7 +12399,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14273,7 +14273,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14352,7 +14352,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22318,7 +22318,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22634,7 +22634,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22713,7 +22713,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22792,7 +22792,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22871,7 +22871,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23187,7 +23187,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23266,7 +23266,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23503,7 +23503,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23740,7 +23740,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23819,7 +23819,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23977,7 +23977,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24056,7 +24056,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24135,7 +24135,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24372,7 +24372,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24451,7 +24451,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24530,7 +24530,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24688,7 +24688,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24925,7 +24925,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25004,7 +25004,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25162,7 +25162,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25320,7 +25320,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25557,7 +25557,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25634,7 +25634,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25942,7 +25942,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26096,7 +26096,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26173,7 +26173,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26250,7 +26250,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26489,7 +26489,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12399,7 +12399,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14273,7 +14273,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14352,7 +14352,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19024,7 +19024,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19340,7 +19340,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20367,7 +20367,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22318,7 +22318,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22555,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22634,7 +22634,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22713,7 +22713,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22792,7 +22792,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22871,7 +22871,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23187,7 +23187,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23266,7 +23266,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23345,7 +23345,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23503,7 +23503,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23740,7 +23740,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23819,7 +23819,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23977,7 +23977,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24056,7 +24056,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24135,7 +24135,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24372,7 +24372,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24451,7 +24451,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24530,7 +24530,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24688,7 +24688,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24925,7 +24925,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25004,7 +25004,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25162,7 +25162,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25320,7 +25320,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25557,7 +25557,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25634,7 +25634,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25942,7 +25942,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26096,7 +26096,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26173,7 +26173,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26250,7 +26250,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26489,7 +26489,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="N37" s="6" t="n">
-        <v>58.9830508474576</v>
+        <v>57.2343744685675</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="N38" s="6" t="n">
-        <v>58.6571056062582</v>
+        <v>57.0924324017913</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="N39" s="6" t="n">
-        <v>58.3311603650587</v>
+        <v>56.950490335015</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="N40" s="6" t="n">
-        <v>58.0052151238592</v>
+        <v>56.8085482682388</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="N41" s="6" t="n">
-        <v>57.6792698826597</v>
+        <v>56.6666062014625</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="N42" s="6" t="n">
-        <v>57.3533246414602</v>
+        <v>56.5246641346862</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="N43" s="6" t="n">
-        <v>57.0273794002608</v>
+        <v>56.38272206791</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="N44" s="6" t="n">
-        <v>56.7014341590613</v>
+        <v>56.2407800011337</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="N45" s="6" t="n">
-        <v>56.3754889178618</v>
+        <v>56.0988379343575</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="N46" s="6" t="n">
-        <v>56.0495436766623</v>
+        <v>55.9568958675812</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="N47" s="6" t="n">
-        <v>55.7235984354628</v>
+        <v>55.8149538008049</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="N48" s="6" t="n">
-        <v>55.53698769911</v>
+        <v>55.7186440677966</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="N49" s="6" t="n">
-        <v>55.3503769627572</v>
+        <v>55.6223229975625</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="N50" s="6" t="n">
-        <v>55.1637662264044</v>
+        <v>55.5260132645542</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="N51" s="6" t="n">
-        <v>54.9771554900516</v>
+        <v>55.4297035315458</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="N52" s="6" t="n">
-        <v>54.7905447536988</v>
+        <v>55.3333937985375</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="N53" s="6" t="n">
-        <v>54.603934017346</v>
+        <v>55.2370727283034</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="N54" s="6" t="n">
-        <v>54.4173232809931</v>
+        <v>55.140762995295</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="N55" s="6" t="n">
-        <v>54.2307125446403</v>
+        <v>55.0444532622867</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="N56" s="6" t="n">
-        <v>54.0441018082875</v>
+        <v>54.9481321920526</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="N57" s="6" t="n">
-        <v>53.8574910719347</v>
+        <v>54.8518224590443</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="N58" s="6" t="n">
-        <v>53.6711070800975</v>
+        <v>54.737815316592</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="N59" s="6" t="n">
-        <v>53.4847230882603</v>
+        <v>54.623796836914</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="N60" s="6" t="n">
-        <v>53.2983390964231</v>
+        <v>54.5097896944618</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="N61" s="6" t="n">
-        <v>53.1119551045859</v>
+        <v>54.3957712147837</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="N62" s="6" t="n">
-        <v>52.9255711127487</v>
+        <v>54.2817640723315</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="N63" s="6" t="n">
-        <v>52.7671447196871</v>
+        <v>54.1582903463522</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="N64" s="6" t="n">
-        <v>52.6366759254011</v>
+        <v>54.0348279575988</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="N65" s="6" t="n">
-        <v>52.5341647298906</v>
+        <v>53.9113542316195</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="N66" s="6" t="n">
-        <v>52.4596111331557</v>
+        <v>53.7878918428661</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="N67" s="6" t="n">
-        <v>52.4130151351964</v>
+        <v>53.6644181168868</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>52.3477807380534</v>
+        <v>53.608536931013</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="N69" s="6" t="n">
-        <v>52.2949719403662</v>
+        <v>53.5526557451392</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="N70" s="6" t="n">
-        <v>52.2338793719177</v>
+        <v>53.4967632220396</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5703,7 +5703,9 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N71" s="4" t="n"/>
+      <c r="N71" s="6" t="n">
+        <v>53.4408820361657</v>
+      </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5711,7 +5713,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5788,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5865,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5942,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6019,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6096,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6173,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6250,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6327,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6404,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6481,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6558,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6635,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6712,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6789,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6866,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6943,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7020,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7097,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7174,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7251,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7328,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7405,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7482,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7559,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7636,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7713,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7790,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7867,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7944,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8021,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8098,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8252,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8331,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8410,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8491,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8568,7 +8570,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8647,7 +8649,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8726,7 +8728,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8805,7 +8807,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8884,7 +8886,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8963,7 +8965,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9042,7 +9044,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9121,7 +9123,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9200,7 +9202,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9279,7 +9281,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9358,7 +9360,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9437,7 +9439,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9516,7 +9518,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9595,7 +9597,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9674,7 +9676,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9753,7 +9755,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9832,7 +9834,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9911,7 +9913,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9990,7 +9992,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10069,7 +10071,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10148,7 +10150,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10227,7 +10229,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10306,7 +10308,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10385,7 +10387,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10464,7 +10466,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10543,7 +10545,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10622,7 +10624,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10701,7 +10703,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10780,7 +10782,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10859,7 +10861,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10936,7 +10938,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11013,7 +11015,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11090,7 +11092,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11167,7 +11169,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11244,7 +11246,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11321,7 +11323,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11398,7 +11400,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11475,7 +11477,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11552,7 +11554,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11629,7 +11631,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11706,7 +11708,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11783,7 +11785,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11860,7 +11862,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11937,7 +11939,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12014,7 +12016,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12091,7 +12093,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12168,7 +12170,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12247,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12322,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12399,7 +12401,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12476,7 +12478,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12553,7 +12555,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12630,7 +12632,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12707,7 +12709,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12784,7 +12786,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12861,7 +12863,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12938,7 +12940,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13015,7 +13017,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13092,7 +13094,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13169,7 +13171,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13246,7 +13248,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13325,7 +13327,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13404,7 +13406,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13483,7 +13485,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13562,7 +13564,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13641,7 +13643,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13720,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13799,7 +13801,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13878,7 +13880,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13957,7 +13959,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14036,7 +14038,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14115,7 +14117,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14194,7 +14196,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14273,7 +14275,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14352,7 +14354,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14431,7 +14433,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14510,7 +14512,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14589,7 +14591,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14668,7 +14670,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14747,7 +14749,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14826,7 +14828,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14905,7 +14907,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14984,7 +14986,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15063,7 +15065,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15142,7 +15144,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15221,7 +15223,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15300,7 +15302,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15379,7 +15381,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15458,7 +15460,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15537,7 +15539,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15616,7 +15618,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15695,7 +15697,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15774,7 +15776,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15851,7 +15853,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15928,7 +15930,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16005,7 +16007,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16082,7 +16084,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16159,7 +16161,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16236,7 +16238,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16313,7 +16315,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16390,7 +16392,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16467,7 +16469,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16544,7 +16546,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16621,7 +16623,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16698,7 +16700,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16775,7 +16777,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16852,7 +16854,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16929,7 +16931,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17006,7 +17008,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17083,7 +17085,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17160,7 +17162,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17237,7 +17239,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17314,7 +17316,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17391,7 +17393,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17468,7 +17470,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17545,7 +17547,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17622,7 +17624,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17699,7 +17701,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17776,7 +17778,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17853,7 +17855,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17930,7 +17932,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18007,7 +18009,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18084,7 +18086,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18161,7 +18163,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18238,7 +18240,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18315,7 +18317,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18392,7 +18394,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18462,7 +18464,7 @@
         </is>
       </c>
       <c r="N235" s="6" t="n">
-        <v>1997.56479057799</v>
+        <v>1999.5645080765</v>
       </c>
       <c r="O235" s="4" t="inlineStr">
         <is>
@@ -18471,7 +18473,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18541,7 +18543,7 @@
         </is>
       </c>
       <c r="N236" s="6" t="n">
-        <v>2037.30182520885</v>
+        <v>2039.09214934873</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -18550,7 +18552,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18620,7 +18622,7 @@
         </is>
       </c>
       <c r="N237" s="6" t="n">
-        <v>2226.55481105961</v>
+        <v>2228.30297292773</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
@@ -18629,7 +18631,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18699,7 +18701,7 @@
         </is>
       </c>
       <c r="N238" s="6" t="n">
-        <v>2027.59967205093</v>
+        <v>2029.79546326151</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -18708,7 +18710,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18778,7 +18780,7 @@
         </is>
       </c>
       <c r="N239" s="6" t="n">
-        <v>2299.11785137022</v>
+        <v>2300.75265355599</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
@@ -18787,7 +18789,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18857,7 +18859,7 @@
         </is>
       </c>
       <c r="N240" s="6" t="n">
-        <v>2111.33770063193</v>
+        <v>2115.87811229818</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -18866,7 +18868,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18936,7 +18938,7 @@
         </is>
       </c>
       <c r="N241" s="6" t="n">
-        <v>2203.62644762536</v>
+        <v>2208.49145142634</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
@@ -18945,7 +18947,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19015,7 +19017,7 @@
         </is>
       </c>
       <c r="N242" s="6" t="n">
-        <v>2149.90770739915</v>
+        <v>2153.54950641814</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -19024,7 +19026,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19094,7 +19096,7 @@
         </is>
       </c>
       <c r="N243" s="6" t="n">
-        <v>2218.43187719732</v>
+        <v>2220.82930887295</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
@@ -19103,7 +19105,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19173,7 +19175,7 @@
         </is>
       </c>
       <c r="N244" s="6" t="n">
-        <v>2399.16210710328</v>
+        <v>2401.35837131582</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19182,7 +19184,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19252,7 +19254,7 @@
         </is>
       </c>
       <c r="N245" s="6" t="n">
-        <v>2391.36796026802</v>
+        <v>2394.28162859526</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
@@ -19261,7 +19263,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19331,7 +19333,7 @@
         </is>
       </c>
       <c r="N246" s="6" t="n">
-        <v>2188.40606705914</v>
+        <v>2191.32232910637</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -19340,7 +19342,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19410,7 +19412,7 @@
         </is>
       </c>
       <c r="N247" s="6" t="n">
-        <v>2648.88652521803</v>
+        <v>2650.38144417429</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19419,7 +19421,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19489,7 +19491,7 @@
         </is>
       </c>
       <c r="N248" s="6" t="n">
-        <v>2432.12630470112</v>
+        <v>2433.65756309621</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19498,7 +19500,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19568,7 +19570,7 @@
         </is>
       </c>
       <c r="N249" s="6" t="n">
-        <v>2305.02805179379</v>
+        <v>2306.72277001345</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19577,7 +19579,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19647,7 +19649,7 @@
         </is>
       </c>
       <c r="N250" s="6" t="n">
-        <v>2371.58340737061</v>
+        <v>2373.23927265671</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19656,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19726,7 +19728,7 @@
         </is>
       </c>
       <c r="N251" s="6" t="n">
-        <v>2377.64028480756</v>
+        <v>2379.06855149063</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19735,7 +19737,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19805,7 +19807,7 @@
         </is>
       </c>
       <c r="N252" s="6" t="n">
-        <v>2391.33788149518</v>
+        <v>2393.2340074316</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -19814,7 +19816,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19884,7 +19886,7 @@
         </is>
       </c>
       <c r="N253" s="6" t="n">
-        <v>2346.01163837283</v>
+        <v>2347.16952651496</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
@@ -19893,7 +19895,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19963,7 +19965,7 @@
         </is>
       </c>
       <c r="N254" s="6" t="n">
-        <v>2231.75458660546</v>
+        <v>2232.46847958222</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -19972,7 +19974,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20042,7 +20044,7 @@
         </is>
       </c>
       <c r="N255" s="6" t="n">
-        <v>2621.20702328211</v>
+        <v>2621.77236646228</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
@@ -20051,7 +20053,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20121,7 +20123,7 @@
         </is>
       </c>
       <c r="N256" s="6" t="n">
-        <v>2309.9066118944</v>
+        <v>2310.76018208667</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
@@ -20130,7 +20132,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20200,7 +20202,7 @@
         </is>
       </c>
       <c r="N257" s="6" t="n">
-        <v>2310.75269478151</v>
+        <v>2311.30306025908</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20209,7 +20211,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20279,7 +20281,7 @@
         </is>
       </c>
       <c r="N258" s="6" t="n">
-        <v>2529.2097489945</v>
+        <v>2529.75352065448</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
@@ -20288,7 +20290,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20358,7 +20360,7 @@
         </is>
       </c>
       <c r="N259" s="6" t="n">
-        <v>2173.57093050952</v>
+        <v>2174.10934683844</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20367,7 +20369,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20437,7 +20439,7 @@
         </is>
       </c>
       <c r="N260" s="6" t="n">
-        <v>2098.46944015591</v>
+        <v>2099.62250114328</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
@@ -20446,7 +20448,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20516,7 +20518,7 @@
         </is>
       </c>
       <c r="N261" s="6" t="n">
-        <v>2009.0681450604</v>
+        <v>2009.28862497975</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
@@ -20525,7 +20527,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20595,7 +20597,7 @@
         </is>
       </c>
       <c r="N262" s="6" t="n">
-        <v>1933.19114696252</v>
+        <v>1933.59827078759</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
@@ -20604,7 +20606,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20674,7 +20676,7 @@
         </is>
       </c>
       <c r="N263" s="6" t="n">
-        <v>1451.3949056587</v>
+        <v>1449.82357174053</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
@@ -20683,7 +20685,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20753,7 +20755,7 @@
         </is>
       </c>
       <c r="N264" s="6" t="n">
-        <v>1379.73439965</v>
+        <v>1378.68040429069</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
@@ -20762,7 +20764,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20832,7 +20834,7 @@
         </is>
       </c>
       <c r="N265" s="6" t="n">
-        <v>1093.43160664363</v>
+        <v>1093.07473267628</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
@@ -20841,7 +20843,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20911,7 +20913,7 @@
         </is>
       </c>
       <c r="N266" s="6" t="n">
-        <v>1409.82623845927</v>
+        <v>1410.4310117024</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
@@ -20920,7 +20922,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20990,7 +20992,7 @@
         </is>
       </c>
       <c r="N267" s="6" t="n">
-        <v>1364.68351163595</v>
+        <v>1365.21601076207</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
@@ -20999,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21069,7 +21071,7 @@
         </is>
       </c>
       <c r="N268" s="6" t="n">
-        <v>1331.23284099658</v>
+        <v>1330.7019945812</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
@@ -21078,7 +21080,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21147,7 +21149,9 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N269" s="4" t="n"/>
+      <c r="N269" s="6" t="n">
+        <v>1457.49043766322</v>
+      </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21155,7 +21159,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21313,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21390,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21467,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21544,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21621,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21698,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21775,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21852,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21929,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22006,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22085,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22164,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22243,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22318,7 +22322,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22397,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22476,7 +22480,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22555,7 +22559,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22634,7 +22638,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22713,7 +22717,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22792,7 +22796,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22871,7 +22875,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22950,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23029,7 +23033,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23112,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23187,7 +23191,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23266,7 +23270,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23345,7 +23349,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23424,7 +23428,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23503,7 +23507,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23582,7 +23586,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23661,7 +23665,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23740,7 +23744,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23819,7 +23823,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23902,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23977,7 +23981,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24056,7 +24060,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24135,7 +24139,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24214,7 +24218,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24293,7 +24297,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24372,7 +24376,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24451,7 +24455,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24530,7 +24534,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24609,7 +24613,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24688,7 +24692,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24767,7 +24771,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24846,7 +24850,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24925,7 +24929,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25004,7 +25008,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25083,7 +25087,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25162,7 +25166,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25241,7 +25245,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25320,7 +25324,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25399,7 +25403,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25478,7 +25482,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25557,7 +25561,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25634,7 +25638,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25711,7 +25715,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25788,7 +25792,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25865,7 +25869,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25942,7 +25946,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26019,7 +26023,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26096,7 +26100,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26173,7 +26177,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26250,7 +26254,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26327,7 +26331,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26404,7 +26408,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26489,7 +26493,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9913,7 +9913,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10861,7 +10861,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12940,7 +12940,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13171,7 +13171,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14038,7 +14038,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14117,7 +14117,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14196,7 +14196,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14275,7 +14275,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14512,7 +14512,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14749,7 +14749,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14907,7 +14907,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15460,7 +15460,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15539,7 +15539,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16161,7 +16161,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16546,7 +16546,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16623,7 +16623,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16700,7 +16700,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16854,7 +16854,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17085,7 +17085,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17239,7 +17239,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17470,7 +17470,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17701,7 +17701,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17932,7 +17932,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18009,7 +18009,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18163,7 +18163,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18240,7 +18240,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18317,7 +18317,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18631,7 +18631,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18789,7 +18789,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19026,7 +19026,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19184,7 +19184,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19263,7 +19263,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19500,7 +19500,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19816,7 +19816,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19895,7 +19895,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19974,7 +19974,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20053,7 +20053,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20132,7 +20132,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20211,7 +20211,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20527,7 +20527,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20606,7 +20606,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20764,7 +20764,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20922,7 +20922,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21390,7 +21390,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21544,7 +21544,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21698,7 +21698,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22164,7 +22164,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22243,7 +22243,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22322,7 +22322,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22717,7 +22717,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22796,7 +22796,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22875,7 +22875,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23033,7 +23033,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23112,7 +23112,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23191,7 +23191,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23349,7 +23349,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23428,7 +23428,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23586,7 +23586,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23665,7 +23665,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23823,7 +23823,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23981,7 +23981,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24060,7 +24060,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24139,7 +24139,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24297,7 +24297,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24613,7 +24613,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24692,7 +24692,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24850,7 +24850,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25008,7 +25008,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25166,7 +25166,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25245,7 +25245,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25324,7 +25324,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25482,7 +25482,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25638,7 +25638,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25715,7 +25715,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25792,7 +25792,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25869,7 +25869,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25946,7 +25946,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26023,7 +26023,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26100,7 +26100,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26177,7 +26177,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26254,7 +26254,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26408,7 +26408,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26493,7 +26493,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_energia_y_ambiente.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q336"/>
+  <dimension ref="A1:Q337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,10 +715,14 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -792,10 +796,14 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -869,10 +877,14 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -946,10 +958,14 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1023,10 +1039,14 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1100,10 +1120,14 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1177,10 +1201,14 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1254,10 +1282,14 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1331,10 +1363,14 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1408,10 +1444,14 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1485,10 +1525,14 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1562,10 +1606,14 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1639,10 +1687,14 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1716,10 +1768,14 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1793,10 +1849,14 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1870,10 +1930,14 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1947,10 +2011,14 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2024,10 +2092,14 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2101,10 +2173,14 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2178,10 +2254,14 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2255,10 +2335,14 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2332,10 +2416,14 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2409,10 +2497,14 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2486,10 +2578,14 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2563,10 +2659,14 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2640,10 +2740,14 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2717,10 +2821,14 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2794,10 +2902,14 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2871,10 +2983,14 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2948,10 +3064,14 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3017,9 +3137,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N37" s="6" t="n">
-        <v>57.2343744685675</v>
-      </c>
+      <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3027,10 +3145,14 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3096,9 +3218,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N38" s="6" t="n">
-        <v>57.0924324017913</v>
-      </c>
+      <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3106,10 +3226,14 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3175,9 +3299,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N39" s="6" t="n">
-        <v>56.950490335015</v>
-      </c>
+      <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3185,10 +3307,14 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3254,9 +3380,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N40" s="6" t="n">
-        <v>56.8085482682388</v>
-      </c>
+      <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3264,10 +3388,14 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3333,9 +3461,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N41" s="6" t="n">
-        <v>56.6666062014625</v>
-      </c>
+      <c r="N41" s="4" t="n"/>
       <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3343,10 +3469,14 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3412,9 +3542,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N42" s="6" t="n">
-        <v>56.5246641346862</v>
-      </c>
+      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3422,10 +3550,14 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q42" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3491,9 +3623,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N43" s="6" t="n">
-        <v>56.38272206791</v>
-      </c>
+      <c r="N43" s="4" t="n"/>
       <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3501,10 +3631,14 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3570,9 +3704,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N44" s="6" t="n">
-        <v>56.2407800011337</v>
-      </c>
+      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3580,10 +3712,14 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3649,9 +3785,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N45" s="6" t="n">
-        <v>56.0988379343575</v>
-      </c>
+      <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3659,10 +3793,14 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q45" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -3728,9 +3866,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N46" s="6" t="n">
-        <v>55.9568958675812</v>
-      </c>
+      <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3738,10 +3874,14 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3807,9 +3947,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N47" s="6" t="n">
-        <v>55.8149538008049</v>
-      </c>
+      <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3817,10 +3955,14 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -3886,9 +4028,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N48" s="6" t="n">
-        <v>55.7186440677966</v>
-      </c>
+      <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3896,10 +4036,14 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -3965,9 +4109,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N49" s="6" t="n">
-        <v>55.6223229975625</v>
-      </c>
+      <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -3975,10 +4117,14 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q49" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4044,9 +4190,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N50" s="6" t="n">
-        <v>55.5260132645542</v>
-      </c>
+      <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4054,10 +4198,14 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4123,9 +4271,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N51" s="6" t="n">
-        <v>55.4297035315458</v>
-      </c>
+      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4133,10 +4279,14 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q51" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4202,9 +4352,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N52" s="6" t="n">
-        <v>55.3333937985375</v>
-      </c>
+      <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4212,10 +4360,14 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4281,9 +4433,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N53" s="6" t="n">
-        <v>55.2370727283034</v>
-      </c>
+      <c r="N53" s="4" t="n"/>
       <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4291,10 +4441,14 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4360,9 +4514,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N54" s="6" t="n">
-        <v>55.140762995295</v>
-      </c>
+      <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4370,10 +4522,14 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4439,9 +4595,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N55" s="6" t="n">
-        <v>55.0444532622867</v>
-      </c>
+      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4449,10 +4603,14 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -4518,9 +4676,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N56" s="6" t="n">
-        <v>54.9481321920526</v>
-      </c>
+      <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4528,10 +4684,14 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4597,9 +4757,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N57" s="6" t="n">
-        <v>54.8518224590443</v>
-      </c>
+      <c r="N57" s="4" t="n"/>
       <c r="O57" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4607,10 +4765,14 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -4676,9 +4838,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N58" s="6" t="n">
-        <v>54.737815316592</v>
-      </c>
+      <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4686,10 +4846,14 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4755,9 +4919,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N59" s="6" t="n">
-        <v>54.623796836914</v>
-      </c>
+      <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4765,10 +4927,14 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -4834,9 +5000,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N60" s="6" t="n">
-        <v>54.5097896944618</v>
-      </c>
+      <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4844,10 +5008,14 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -4913,9 +5081,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N61" s="6" t="n">
-        <v>54.3957712147837</v>
-      </c>
+      <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -4923,10 +5089,14 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q61" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -4992,9 +5162,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N62" s="6" t="n">
-        <v>54.2817640723315</v>
-      </c>
+      <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5002,10 +5170,14 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q62" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -5071,9 +5243,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N63" s="6" t="n">
-        <v>54.1582903463522</v>
-      </c>
+      <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5081,10 +5251,14 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q63" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -5150,9 +5324,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N64" s="6" t="n">
-        <v>54.0348279575988</v>
-      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5160,10 +5332,14 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q64" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5229,9 +5405,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N65" s="6" t="n">
-        <v>53.9113542316195</v>
-      </c>
+      <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5239,10 +5413,14 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q65" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -5308,9 +5486,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N66" s="6" t="n">
-        <v>53.7878918428661</v>
-      </c>
+      <c r="N66" s="4" t="n"/>
       <c r="O66" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5318,10 +5494,14 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q66" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -5387,9 +5567,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N67" s="6" t="n">
-        <v>53.6644181168868</v>
-      </c>
+      <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5397,10 +5575,14 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q67" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -5466,9 +5648,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N68" s="6" t="n">
-        <v>53.608536931013</v>
-      </c>
+      <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5476,10 +5656,14 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q68" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5545,9 +5729,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N69" s="6" t="n">
-        <v>53.5526557451392</v>
-      </c>
+      <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5555,10 +5737,14 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q69" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -5624,9 +5810,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N70" s="6" t="n">
-        <v>53.4967632220396</v>
-      </c>
+      <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5634,10 +5818,14 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q70" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5703,9 +5891,7 @@
           <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
-      <c r="N71" s="6" t="n">
-        <v>53.4408820361657</v>
-      </c>
+      <c r="N71" s="4" t="n"/>
       <c r="O71" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5713,10 +5899,14 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q71" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -5790,10 +5980,14 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -5827,7 +6021,7 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -5841,22 +6035,22 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Bosques</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>electricidad</t>
+          <t>bosques</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.ACCS.ZS</t>
+          <t>AG.LND.FRST.ZS</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>Acceso a electricidad</t>
+          <t>Superficie forestal como porcentaje del territorio</t>
         </is>
       </c>
       <c r="N73" s="4" t="n"/>
@@ -5867,10 +6061,14 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="n"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5904,7 +6102,7 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
@@ -5944,7 +6142,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5981,7 +6179,7 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -6021,7 +6219,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6058,7 +6256,7 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -6098,7 +6296,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6135,7 +6333,7 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -6175,7 +6373,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6212,7 +6410,7 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -6252,7 +6450,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6289,7 +6487,7 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -6329,7 +6527,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6366,7 +6564,7 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -6406,7 +6604,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6443,7 +6641,7 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -6483,7 +6681,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6520,7 +6718,7 @@
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
@@ -6560,7 +6758,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6597,7 +6795,7 @@
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -6637,7 +6835,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6872,7 @@
         </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -6714,7 +6912,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6751,7 +6949,7 @@
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -6791,7 +6989,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6828,7 +7026,7 @@
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
@@ -6868,7 +7066,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6905,7 +7103,7 @@
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -6945,7 +7143,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6982,7 +7180,7 @@
         </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -7022,7 +7220,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7059,7 +7257,7 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -7099,7 +7297,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7136,7 +7334,7 @@
         </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
@@ -7176,7 +7374,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7213,7 +7411,7 @@
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -7253,7 +7451,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7290,7 +7488,7 @@
         </is>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -7330,7 +7528,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7367,7 +7565,7 @@
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -7407,7 +7605,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7444,7 +7642,7 @@
         </is>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
@@ -7484,7 +7682,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7521,7 +7719,7 @@
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -7561,7 +7759,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7598,7 +7796,7 @@
         </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
@@ -7638,7 +7836,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7675,7 +7873,7 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -7715,7 +7913,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7752,7 +7950,7 @@
         </is>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
@@ -7792,7 +7990,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7829,7 +8027,7 @@
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -7869,7 +8067,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7906,7 +8104,7 @@
         </is>
       </c>
       <c r="G100" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
@@ -7946,7 +8144,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7983,7 +8181,7 @@
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -8023,7 +8221,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8060,7 +8258,7 @@
         </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
@@ -8100,7 +8298,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8137,7 +8335,7 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -8177,7 +8375,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8214,7 +8412,7 @@
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
@@ -8254,7 +8452,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8291,7 +8489,7 @@
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -8323,9 +8521,7 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N105" s="6" t="n">
-        <v>97.82020300000001</v>
-      </c>
+      <c r="N105" s="4" t="n"/>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -8333,7 +8529,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8370,7 +8566,7 @@
         </is>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
@@ -8403,7 +8599,7 @@
         </is>
       </c>
       <c r="N106" s="6" t="n">
-        <v>98.2395324707031</v>
+        <v>97.82020300000001</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
@@ -8412,7 +8608,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8449,7 +8645,7 @@
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -8482,7 +8678,7 @@
         </is>
       </c>
       <c r="N107" s="6" t="n">
-        <v>98.3233337402344</v>
+        <v>98.2395324707031</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
@@ -8491,7 +8687,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8528,7 +8724,7 @@
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
@@ -8560,8 +8756,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N108" s="5" t="n">
-        <v>99</v>
+      <c r="N108" s="6" t="n">
+        <v>98.3233337402344</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
@@ -8570,7 +8766,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8607,7 +8803,7 @@
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -8639,8 +8835,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N109" s="6" t="n">
-        <v>98.484130859375</v>
+      <c r="N109" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
@@ -8649,7 +8845,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8686,7 +8882,7 @@
         </is>
       </c>
       <c r="G110" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
@@ -8719,7 +8915,7 @@
         </is>
       </c>
       <c r="N110" s="6" t="n">
-        <v>98.7</v>
+        <v>98.484130859375</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
@@ -8728,7 +8924,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8765,7 +8961,7 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -8798,7 +8994,7 @@
         </is>
       </c>
       <c r="N111" s="6" t="n">
-        <v>98.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
@@ -8807,7 +9003,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8844,7 +9040,7 @@
         </is>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
@@ -8877,7 +9073,7 @@
         </is>
       </c>
       <c r="N112" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
@@ -8886,7 +9082,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8923,7 +9119,7 @@
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -8965,7 +9161,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9002,7 +9198,7 @@
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
@@ -9035,7 +9231,7 @@
         </is>
       </c>
       <c r="N114" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
@@ -9044,7 +9240,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9081,7 +9277,7 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -9114,7 +9310,7 @@
         </is>
       </c>
       <c r="N115" s="6" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
@@ -9123,7 +9319,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9160,7 +9356,7 @@
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -9193,7 +9389,7 @@
         </is>
       </c>
       <c r="N116" s="6" t="n">
-        <v>95.7</v>
+        <v>99.8</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
@@ -9202,7 +9398,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9239,7 +9435,7 @@
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -9272,7 +9468,7 @@
         </is>
       </c>
       <c r="N117" s="6" t="n">
-        <v>99.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
@@ -9281,7 +9477,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9318,7 +9514,7 @@
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
@@ -9351,7 +9547,7 @@
         </is>
       </c>
       <c r="N118" s="6" t="n">
-        <v>98.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
@@ -9360,7 +9556,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9397,7 +9593,7 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -9430,7 +9626,7 @@
         </is>
       </c>
       <c r="N119" s="6" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
@@ -9439,7 +9635,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9476,7 +9672,7 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
@@ -9509,7 +9705,7 @@
         </is>
       </c>
       <c r="N120" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
@@ -9518,7 +9714,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9555,7 +9751,7 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -9597,7 +9793,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9634,7 +9830,7 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
@@ -9666,8 +9862,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N122" s="5" t="n">
-        <v>99</v>
+      <c r="N122" s="6" t="n">
+        <v>98.90000000000001</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
@@ -9676,7 +9872,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9713,7 +9909,7 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -9745,8 +9941,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N123" s="6" t="n">
-        <v>99.09999999999999</v>
+      <c r="N123" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
@@ -9755,7 +9951,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9792,7 +9988,7 @@
         </is>
       </c>
       <c r="G124" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
@@ -9825,7 +10021,7 @@
         </is>
       </c>
       <c r="N124" s="6" t="n">
-        <v>98.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
@@ -9834,7 +10030,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9871,7 +10067,7 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -9904,7 +10100,7 @@
         </is>
       </c>
       <c r="N125" s="6" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
@@ -9913,7 +10109,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9950,7 +10146,7 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
@@ -9983,7 +10179,7 @@
         </is>
       </c>
       <c r="N126" s="6" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
@@ -9992,7 +10188,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10029,7 +10225,7 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -10061,8 +10257,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N127" s="5" t="n">
-        <v>100</v>
+      <c r="N127" s="6" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
@@ -10071,7 +10267,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10108,7 +10304,7 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
@@ -10150,7 +10346,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10187,7 +10383,7 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -10219,8 +10415,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N129" s="6" t="n">
-        <v>99.40000000000001</v>
+      <c r="N129" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
@@ -10229,7 +10425,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10266,7 +10462,7 @@
         </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
@@ -10299,7 +10495,7 @@
         </is>
       </c>
       <c r="N130" s="6" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
@@ -10308,7 +10504,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10345,7 +10541,7 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -10378,7 +10574,7 @@
         </is>
       </c>
       <c r="N131" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
@@ -10387,7 +10583,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10424,7 +10620,7 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
@@ -10457,7 +10653,7 @@
         </is>
       </c>
       <c r="N132" s="6" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
@@ -10466,7 +10662,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10503,7 +10699,7 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -10536,7 +10732,7 @@
         </is>
       </c>
       <c r="N133" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
@@ -10545,7 +10741,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10582,7 +10778,7 @@
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
@@ -10614,8 +10810,8 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N134" s="5" t="n">
-        <v>100</v>
+      <c r="N134" s="6" t="n">
+        <v>99.90000000000001</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
@@ -10624,7 +10820,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10661,7 +10857,7 @@
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -10703,7 +10899,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10740,7 +10936,7 @@
         </is>
       </c>
       <c r="G136" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
@@ -10782,7 +10978,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10819,7 +11015,7 @@
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -10861,7 +11057,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10898,7 +11094,7 @@
         </is>
       </c>
       <c r="G138" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
@@ -10930,7 +11126,9 @@
           <t>Acceso a electricidad</t>
         </is>
       </c>
-      <c r="N138" s="4" t="n"/>
+      <c r="N138" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10938,7 +11136,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10975,7 +11173,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -10999,12 +11197,12 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>EG.ELC.RNEW.ZS</t>
+          <t>EG.ELC.ACCS.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
+          <t>Acceso a electricidad</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11015,7 +11213,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11052,7 +11250,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11092,7 +11290,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11129,7 +11327,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11169,7 +11367,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11206,7 +11404,7 @@
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11246,7 +11444,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11283,7 +11481,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11323,7 +11521,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11360,7 +11558,7 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11400,7 +11598,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11437,7 +11635,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11477,7 +11675,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11514,7 +11712,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11554,7 +11752,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11591,7 +11789,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11631,7 +11829,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11668,7 +11866,7 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11708,7 +11906,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11745,7 +11943,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11785,7 +11983,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11822,7 +12020,7 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -11862,7 +12060,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11899,7 +12097,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -11939,7 +12137,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11976,7 +12174,7 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12016,7 +12214,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12053,7 +12251,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12093,7 +12291,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12130,7 +12328,7 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12170,7 +12368,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12207,7 +12405,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12247,7 +12445,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12284,7 +12482,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12324,7 +12522,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12361,7 +12559,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12401,7 +12599,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12438,7 +12636,7 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12478,7 +12676,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12515,7 +12713,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12555,7 +12753,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12592,7 +12790,7 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12632,7 +12830,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12669,7 +12867,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12709,7 +12907,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12746,7 +12944,7 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -12786,7 +12984,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12823,7 +13021,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -12863,7 +13061,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12900,7 +13098,7 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -12940,7 +13138,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12977,7 +13175,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13017,7 +13215,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13054,7 +13252,7 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13094,7 +13292,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13131,7 +13329,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13171,7 +13369,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13208,7 +13406,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13248,7 +13446,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13285,7 +13483,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13317,9 +13515,7 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N169" s="6" t="n">
-        <v>62.3438579929536</v>
-      </c>
+      <c r="N169" s="4" t="n"/>
       <c r="O169" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -13327,7 +13523,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13364,7 +13560,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13397,7 +13593,7 @@
         </is>
       </c>
       <c r="N170" s="6" t="n">
-        <v>70.3254022135561</v>
+        <v>62.3438579929536</v>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
@@ -13406,7 +13602,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13443,7 +13639,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13476,7 +13672,7 @@
         </is>
       </c>
       <c r="N171" s="6" t="n">
-        <v>70.09341637010679</v>
+        <v>70.3254022135561</v>
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
@@ -13485,7 +13681,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13522,7 +13718,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13555,7 +13751,7 @@
         </is>
       </c>
       <c r="N172" s="6" t="n">
-        <v>68.42985212302899</v>
+        <v>70.09341637010679</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
@@ -13564,7 +13760,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13601,7 +13797,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13634,7 +13830,7 @@
         </is>
       </c>
       <c r="N173" s="6" t="n">
-        <v>72.0068519116553</v>
+        <v>68.42985212302899</v>
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
@@ -13643,7 +13839,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13680,7 +13876,7 @@
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13713,7 +13909,7 @@
         </is>
       </c>
       <c r="N174" s="6" t="n">
-        <v>70.0514663834654</v>
+        <v>72.0068519116553</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
@@ -13722,7 +13918,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13759,7 +13955,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -13792,7 +13988,7 @@
         </is>
       </c>
       <c r="N175" s="6" t="n">
-        <v>71.237498015558</v>
+        <v>70.0514663834654</v>
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
@@ -13801,7 +13997,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13838,7 +14034,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -13871,7 +14067,7 @@
         </is>
       </c>
       <c r="N176" s="6" t="n">
-        <v>73.359380003843</v>
+        <v>71.237498015558</v>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
@@ -13880,7 +14076,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13917,7 +14113,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -13950,7 +14146,7 @@
         </is>
       </c>
       <c r="N177" s="6" t="n">
-        <v>71.59649946849279</v>
+        <v>73.359380003843</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
@@ -13959,7 +14155,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13996,7 +14192,7 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14029,7 +14225,7 @@
         </is>
       </c>
       <c r="N178" s="6" t="n">
-        <v>75.1646552472619</v>
+        <v>71.59649946849279</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
@@ -14038,7 +14234,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14075,7 +14271,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14108,7 +14304,7 @@
         </is>
       </c>
       <c r="N179" s="6" t="n">
-        <v>73.7484021531353</v>
+        <v>75.1646552472619</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
@@ -14117,7 +14313,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14154,7 +14350,7 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14187,7 +14383,7 @@
         </is>
       </c>
       <c r="N180" s="6" t="n">
-        <v>67.0679878826884</v>
+        <v>73.7484021531353</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
@@ -14196,7 +14392,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14233,7 +14429,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14266,7 +14462,7 @@
         </is>
       </c>
       <c r="N181" s="6" t="n">
-        <v>64.8151373949397</v>
+        <v>67.0679878826884</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
@@ -14275,7 +14471,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14312,7 +14508,7 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14345,7 +14541,7 @@
         </is>
       </c>
       <c r="N182" s="6" t="n">
-        <v>65.83572609414431</v>
+        <v>64.8151373949397</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
@@ -14354,7 +14550,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14391,7 +14587,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14424,7 +14620,7 @@
         </is>
       </c>
       <c r="N183" s="6" t="n">
-        <v>70.94119195375541</v>
+        <v>65.83572609414431</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
@@ -14433,7 +14629,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14470,7 +14666,7 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14503,7 +14699,7 @@
         </is>
       </c>
       <c r="N184" s="6" t="n">
-        <v>73.28606809382831</v>
+        <v>70.94119195375541</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
@@ -14512,7 +14708,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14549,7 +14745,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14582,7 +14778,7 @@
         </is>
       </c>
       <c r="N185" s="6" t="n">
-        <v>73.9008893155349</v>
+        <v>73.28606809382831</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
@@ -14591,7 +14787,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14628,7 +14824,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14661,7 +14857,7 @@
         </is>
       </c>
       <c r="N186" s="6" t="n">
-        <v>72.7246397114189</v>
+        <v>73.9008893155349</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
@@ -14670,7 +14866,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14707,7 +14903,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14740,7 +14936,7 @@
         </is>
       </c>
       <c r="N187" s="6" t="n">
-        <v>72.7965497875051</v>
+        <v>72.7246397114189</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
@@ -14749,7 +14945,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14786,7 +14982,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -14819,7 +15015,7 @@
         </is>
       </c>
       <c r="N188" s="6" t="n">
-        <v>71.6609231333517</v>
+        <v>72.7965497875051</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -14828,7 +15024,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14865,7 +15061,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -14898,7 +15094,7 @@
         </is>
       </c>
       <c r="N189" s="6" t="n">
-        <v>67.242625937084</v>
+        <v>71.6609231333517</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
@@ -14907,7 +15103,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14944,7 +15140,7 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -14977,7 +15173,7 @@
         </is>
       </c>
       <c r="N190" s="6" t="n">
-        <v>70.7004672541846</v>
+        <v>67.242625937084</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
@@ -14986,7 +15182,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15023,7 +15219,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15056,7 +15252,7 @@
         </is>
       </c>
       <c r="N191" s="6" t="n">
-        <v>67.0600784236679</v>
+        <v>70.7004672541846</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
@@ -15065,7 +15261,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15102,7 +15298,7 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15135,7 +15331,7 @@
         </is>
       </c>
       <c r="N192" s="6" t="n">
-        <v>65.96440553278519</v>
+        <v>67.0600784236679</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
@@ -15144,7 +15340,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15181,7 +15377,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15214,7 +15410,7 @@
         </is>
       </c>
       <c r="N193" s="6" t="n">
-        <v>77.5369122989602</v>
+        <v>65.96440553278519</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
@@ -15223,7 +15419,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15260,7 +15456,7 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15293,7 +15489,7 @@
         </is>
       </c>
       <c r="N194" s="6" t="n">
-        <v>65.53966478494149</v>
+        <v>77.5369122989602</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
@@ -15302,7 +15498,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15339,7 +15535,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15372,7 +15568,7 @@
         </is>
       </c>
       <c r="N195" s="6" t="n">
-        <v>62.32403609516</v>
+        <v>65.53966478494149</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
@@ -15381,7 +15577,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15418,7 +15614,7 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15451,7 +15647,7 @@
         </is>
       </c>
       <c r="N196" s="6" t="n">
-        <v>51.4746640846626</v>
+        <v>62.32403609516</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -15460,7 +15656,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15497,7 +15693,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15530,7 +15726,7 @@
         </is>
       </c>
       <c r="N197" s="6" t="n">
-        <v>63.2932794208759</v>
+        <v>51.4746640846626</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
@@ -15539,7 +15735,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15576,7 +15772,7 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15609,7 +15805,7 @@
         </is>
       </c>
       <c r="N198" s="6" t="n">
-        <v>65.9218035546249</v>
+        <v>63.2932794208759</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
@@ -15618,7 +15814,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15655,7 +15851,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15688,7 +15884,7 @@
         </is>
       </c>
       <c r="N199" s="6" t="n">
-        <v>84.45121523562889</v>
+        <v>65.9218035546249</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
         <is>
@@ -15697,7 +15893,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15734,7 +15930,7 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15767,7 +15963,7 @@
         </is>
       </c>
       <c r="N200" s="6" t="n">
-        <v>81.72207575243419</v>
+        <v>84.45121523562889</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
@@ -15776,7 +15972,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15813,7 +16009,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -15845,7 +16041,9 @@
           <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
-      <c r="N201" s="4" t="n"/>
+      <c r="N201" s="6" t="n">
+        <v>81.72207575243419</v>
+      </c>
       <c r="O201" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -15853,7 +16051,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15890,7 +16088,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -15930,7 +16128,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15967,7 +16165,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16007,7 +16205,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16044,7 +16242,7 @@
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16084,7 +16282,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16121,7 +16319,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16135,22 +16333,22 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Electricidad</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>electricidad</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>EG.USE.PCAP.KG.OE</t>
+          <t>EG.ELC.RNEW.ZS</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Uso de energía per cápita</t>
+          <t>Electricidad renovable como porcentaje de la producción eléctrica</t>
         </is>
       </c>
       <c r="N205" s="4" t="n"/>
@@ -16161,7 +16359,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16198,7 +16396,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16238,7 +16436,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16275,7 +16473,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16315,7 +16513,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16352,7 +16550,7 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16392,7 +16590,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16429,7 +16627,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16469,7 +16667,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16506,7 +16704,7 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16546,7 +16744,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16583,7 +16781,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16623,7 +16821,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16660,7 +16858,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16700,7 +16898,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16737,7 +16935,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16777,7 +16975,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16814,7 +17012,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -16854,7 +17052,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16891,7 +17089,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -16931,7 +17129,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16968,7 +17166,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17008,7 +17206,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17045,7 +17243,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17085,7 +17283,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17122,7 +17320,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17162,7 +17360,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17199,7 +17397,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17239,7 +17437,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17276,7 +17474,7 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17316,7 +17514,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17353,7 +17551,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17393,7 +17591,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17430,7 +17628,7 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17470,7 +17668,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17507,7 +17705,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17547,7 +17745,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17584,7 +17782,7 @@
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17624,7 +17822,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17661,7 +17859,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17701,7 +17899,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17738,7 +17936,7 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17778,7 +17976,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17815,7 +18013,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -17855,7 +18053,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17892,7 +18090,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -17932,7 +18130,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17969,7 +18167,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18009,7 +18207,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18046,7 +18244,7 @@
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18086,7 +18284,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18123,7 +18321,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18163,7 +18361,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18200,7 +18398,7 @@
         </is>
       </c>
       <c r="G232" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18240,7 +18438,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18277,7 +18475,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18317,7 +18515,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18354,7 +18552,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18394,7 +18592,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18431,7 +18629,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18463,9 +18661,7 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N235" s="6" t="n">
-        <v>1999.5645080765</v>
-      </c>
+      <c r="N235" s="4" t="n"/>
       <c r="O235" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -18473,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18510,7 +18706,7 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18543,7 +18739,7 @@
         </is>
       </c>
       <c r="N236" s="6" t="n">
-        <v>2039.09214934873</v>
+        <v>1999.5645080765</v>
       </c>
       <c r="O236" s="4" t="inlineStr">
         <is>
@@ -18552,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18589,7 +18785,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18622,7 +18818,7 @@
         </is>
       </c>
       <c r="N237" s="6" t="n">
-        <v>2228.30297292773</v>
+        <v>2039.09214934873</v>
       </c>
       <c r="O237" s="4" t="inlineStr">
         <is>
@@ -18631,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18668,7 +18864,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18701,7 +18897,7 @@
         </is>
       </c>
       <c r="N238" s="6" t="n">
-        <v>2029.79546326151</v>
+        <v>2228.30297292773</v>
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
@@ -18710,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18747,7 +18943,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18780,7 +18976,7 @@
         </is>
       </c>
       <c r="N239" s="6" t="n">
-        <v>2300.75265355599</v>
+        <v>2029.79546326151</v>
       </c>
       <c r="O239" s="4" t="inlineStr">
         <is>
@@ -18789,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18826,7 +19022,7 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -18859,7 +19055,7 @@
         </is>
       </c>
       <c r="N240" s="6" t="n">
-        <v>2115.87811229818</v>
+        <v>2300.75265355599</v>
       </c>
       <c r="O240" s="4" t="inlineStr">
         <is>
@@ -18868,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18905,7 +19101,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -18938,7 +19134,7 @@
         </is>
       </c>
       <c r="N241" s="6" t="n">
-        <v>2208.49145142634</v>
+        <v>2115.87811229818</v>
       </c>
       <c r="O241" s="4" t="inlineStr">
         <is>
@@ -18947,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18984,7 +19180,7 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19017,7 +19213,7 @@
         </is>
       </c>
       <c r="N242" s="6" t="n">
-        <v>2153.54950641814</v>
+        <v>2208.49145142634</v>
       </c>
       <c r="O242" s="4" t="inlineStr">
         <is>
@@ -19026,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19063,7 +19259,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19096,7 +19292,7 @@
         </is>
       </c>
       <c r="N243" s="6" t="n">
-        <v>2220.82930887295</v>
+        <v>2153.54950641814</v>
       </c>
       <c r="O243" s="4" t="inlineStr">
         <is>
@@ -19105,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19142,7 +19338,7 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19175,7 +19371,7 @@
         </is>
       </c>
       <c r="N244" s="6" t="n">
-        <v>2401.35837131582</v>
+        <v>2220.82930887295</v>
       </c>
       <c r="O244" s="4" t="inlineStr">
         <is>
@@ -19184,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19221,7 +19417,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19254,7 +19450,7 @@
         </is>
       </c>
       <c r="N245" s="6" t="n">
-        <v>2394.28162859526</v>
+        <v>2401.35837131582</v>
       </c>
       <c r="O245" s="4" t="inlineStr">
         <is>
@@ -19263,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19300,7 +19496,7 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19333,7 +19529,7 @@
         </is>
       </c>
       <c r="N246" s="6" t="n">
-        <v>2191.32232910637</v>
+        <v>2394.28162859526</v>
       </c>
       <c r="O246" s="4" t="inlineStr">
         <is>
@@ -19342,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19379,7 +19575,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19412,7 +19608,7 @@
         </is>
       </c>
       <c r="N247" s="6" t="n">
-        <v>2650.38144417429</v>
+        <v>2191.32232910637</v>
       </c>
       <c r="O247" s="4" t="inlineStr">
         <is>
@@ -19421,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19458,7 +19654,7 @@
         </is>
       </c>
       <c r="G248" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19491,7 +19687,7 @@
         </is>
       </c>
       <c r="N248" s="6" t="n">
-        <v>2433.65756309621</v>
+        <v>2650.38144417429</v>
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
@@ -19500,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19537,7 +19733,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19570,7 +19766,7 @@
         </is>
       </c>
       <c r="N249" s="6" t="n">
-        <v>2306.72277001345</v>
+        <v>2433.65756309621</v>
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
@@ -19579,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19616,7 +19812,7 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19649,7 +19845,7 @@
         </is>
       </c>
       <c r="N250" s="6" t="n">
-        <v>2373.23927265671</v>
+        <v>2306.72277001345</v>
       </c>
       <c r="O250" s="4" t="inlineStr">
         <is>
@@ -19658,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19695,7 +19891,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19728,7 +19924,7 @@
         </is>
       </c>
       <c r="N251" s="6" t="n">
-        <v>2379.06855149063</v>
+        <v>2373.23927265671</v>
       </c>
       <c r="O251" s="4" t="inlineStr">
         <is>
@@ -19737,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19774,7 +19970,7 @@
         </is>
       </c>
       <c r="G252" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -19807,7 +20003,7 @@
         </is>
       </c>
       <c r="N252" s="6" t="n">
-        <v>2393.2340074316</v>
+        <v>2379.06855149063</v>
       </c>
       <c r="O252" s="4" t="inlineStr">
         <is>
@@ -19816,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19853,7 +20049,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -19886,7 +20082,7 @@
         </is>
       </c>
       <c r="N253" s="6" t="n">
-        <v>2347.16952651496</v>
+        <v>2393.2340074316</v>
       </c>
       <c r="O253" s="4" t="inlineStr">
         <is>
@@ -19895,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19932,7 +20128,7 @@
         </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -19965,7 +20161,7 @@
         </is>
       </c>
       <c r="N254" s="6" t="n">
-        <v>2232.46847958222</v>
+        <v>2347.16952651496</v>
       </c>
       <c r="O254" s="4" t="inlineStr">
         <is>
@@ -19974,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20011,7 +20207,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20044,7 +20240,7 @@
         </is>
       </c>
       <c r="N255" s="6" t="n">
-        <v>2621.77236646228</v>
+        <v>2232.46847958222</v>
       </c>
       <c r="O255" s="4" t="inlineStr">
         <is>
@@ -20053,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20090,7 +20286,7 @@
         </is>
       </c>
       <c r="G256" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20123,7 +20319,7 @@
         </is>
       </c>
       <c r="N256" s="6" t="n">
-        <v>2310.76018208667</v>
+        <v>2621.77236646228</v>
       </c>
       <c r="O256" s="4" t="inlineStr">
         <is>
@@ -20132,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20169,7 +20365,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20202,7 +20398,7 @@
         </is>
       </c>
       <c r="N257" s="6" t="n">
-        <v>2311.30306025908</v>
+        <v>2310.76018208667</v>
       </c>
       <c r="O257" s="4" t="inlineStr">
         <is>
@@ -20211,7 +20407,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20248,7 +20444,7 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20281,7 +20477,7 @@
         </is>
       </c>
       <c r="N258" s="6" t="n">
-        <v>2529.75352065448</v>
+        <v>2311.30306025908</v>
       </c>
       <c r="O258" s="4" t="inlineStr">
         <is>
@@ -20290,7 +20486,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20327,7 +20523,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20360,7 +20556,7 @@
         </is>
       </c>
       <c r="N259" s="6" t="n">
-        <v>2174.10934683844</v>
+        <v>2529.75352065448</v>
       </c>
       <c r="O259" s="4" t="inlineStr">
         <is>
@@ -20369,7 +20565,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20406,7 +20602,7 @@
         </is>
       </c>
       <c r="G260" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20439,7 +20635,7 @@
         </is>
       </c>
       <c r="N260" s="6" t="n">
-        <v>2099.62250114328</v>
+        <v>2174.10934683844</v>
       </c>
       <c r="O260" s="4" t="inlineStr">
         <is>
@@ -20448,7 +20644,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20485,7 +20681,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20518,7 +20714,7 @@
         </is>
       </c>
       <c r="N261" s="6" t="n">
-        <v>2009.28862497975</v>
+        <v>2099.62250114328</v>
       </c>
       <c r="O261" s="4" t="inlineStr">
         <is>
@@ -20527,7 +20723,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20564,7 +20760,7 @@
         </is>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20597,7 +20793,7 @@
         </is>
       </c>
       <c r="N262" s="6" t="n">
-        <v>1933.59827078759</v>
+        <v>2009.28862497975</v>
       </c>
       <c r="O262" s="4" t="inlineStr">
         <is>
@@ -20606,7 +20802,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20643,7 +20839,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20676,7 +20872,7 @@
         </is>
       </c>
       <c r="N263" s="6" t="n">
-        <v>1449.82357174053</v>
+        <v>1933.59827078759</v>
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
@@ -20685,7 +20881,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20722,7 +20918,7 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20755,7 +20951,7 @@
         </is>
       </c>
       <c r="N264" s="6" t="n">
-        <v>1378.68040429069</v>
+        <v>1449.82357174053</v>
       </c>
       <c r="O264" s="4" t="inlineStr">
         <is>
@@ -20764,7 +20960,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20801,7 +20997,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -20834,7 +21030,7 @@
         </is>
       </c>
       <c r="N265" s="6" t="n">
-        <v>1093.07473267628</v>
+        <v>1378.68040429069</v>
       </c>
       <c r="O265" s="4" t="inlineStr">
         <is>
@@ -20843,7 +21039,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20880,7 +21076,7 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -20913,7 +21109,7 @@
         </is>
       </c>
       <c r="N266" s="6" t="n">
-        <v>1410.4310117024</v>
+        <v>1093.07473267628</v>
       </c>
       <c r="O266" s="4" t="inlineStr">
         <is>
@@ -20922,7 +21118,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20959,7 +21155,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -20992,7 +21188,7 @@
         </is>
       </c>
       <c r="N267" s="6" t="n">
-        <v>1365.21601076207</v>
+        <v>1410.4310117024</v>
       </c>
       <c r="O267" s="4" t="inlineStr">
         <is>
@@ -21001,7 +21197,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21038,7 +21234,7 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21071,7 +21267,7 @@
         </is>
       </c>
       <c r="N268" s="6" t="n">
-        <v>1330.7019945812</v>
+        <v>1365.21601076207</v>
       </c>
       <c r="O268" s="4" t="inlineStr">
         <is>
@@ -21080,7 +21276,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21117,7 +21313,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21150,7 +21346,7 @@
         </is>
       </c>
       <c r="N269" s="6" t="n">
-        <v>1457.49043766322</v>
+        <v>1330.7019945812</v>
       </c>
       <c r="O269" s="4" t="inlineStr">
         <is>
@@ -21159,7 +21355,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21196,7 +21392,7 @@
         </is>
       </c>
       <c r="G270" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21228,7 +21424,9 @@
           <t>Uso de energía per cápita</t>
         </is>
       </c>
-      <c r="N270" s="4" t="n"/>
+      <c r="N270" s="6" t="n">
+        <v>1457.49043766322</v>
+      </c>
       <c r="O270" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -21236,7 +21434,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21273,7 +21471,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
@@ -21287,22 +21485,22 @@
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
-          <t>Recursos naturales</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>recursos_naturales</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>NY.GDP.TOTL.RT.ZS</t>
+          <t>EG.USE.PCAP.KG.OE</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
         <is>
-          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+          <t>Uso de energía per cápita</t>
         </is>
       </c>
       <c r="N271" s="4" t="n"/>
@@ -21313,7 +21511,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21350,7 +21548,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
@@ -21390,7 +21588,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21427,7 +21625,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
@@ -21467,7 +21665,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21504,7 +21702,7 @@
         </is>
       </c>
       <c r="G274" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
@@ -21544,7 +21742,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21581,7 +21779,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
@@ -21621,7 +21819,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21658,7 +21856,7 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
@@ -21698,7 +21896,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21735,7 +21933,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
@@ -21775,7 +21973,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21812,7 +22010,7 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
@@ -21852,7 +22050,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21889,7 +22087,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
@@ -21929,7 +22127,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -21966,7 +22164,7 @@
         </is>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
@@ -22006,7 +22204,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22043,7 +22241,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
@@ -22075,9 +22273,7 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N281" s="6" t="n">
-        <v>5.48772130601331</v>
-      </c>
+      <c r="N281" s="4" t="n"/>
       <c r="O281" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -22085,7 +22281,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22122,7 +22318,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
@@ -22155,7 +22351,7 @@
         </is>
       </c>
       <c r="N282" s="6" t="n">
-        <v>7.38794104909662</v>
+        <v>5.48772130601331</v>
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
@@ -22164,7 +22360,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22201,7 +22397,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
@@ -22234,7 +22430,7 @@
         </is>
       </c>
       <c r="N283" s="6" t="n">
-        <v>7.19271915747182</v>
+        <v>7.38794104909662</v>
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
@@ -22243,7 +22439,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22280,7 +22476,7 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
@@ -22313,7 +22509,7 @@
         </is>
       </c>
       <c r="N284" s="6" t="n">
-        <v>10.7554427076038</v>
+        <v>7.19271915747182</v>
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
@@ -22322,7 +22518,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22359,7 +22555,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H285" s="4" t="inlineStr">
         <is>
@@ -22392,7 +22588,7 @@
         </is>
       </c>
       <c r="N285" s="6" t="n">
-        <v>33.9478841729493</v>
+        <v>10.7554427076038</v>
       </c>
       <c r="O285" s="4" t="inlineStr">
         <is>
@@ -22401,7 +22597,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22438,7 +22634,7 @@
         </is>
       </c>
       <c r="G286" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
@@ -22471,7 +22667,7 @@
         </is>
       </c>
       <c r="N286" s="6" t="n">
-        <v>24.8915014056924</v>
+        <v>33.9478841729493</v>
       </c>
       <c r="O286" s="4" t="inlineStr">
         <is>
@@ -22480,7 +22676,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22517,7 +22713,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
@@ -22550,7 +22746,7 @@
         </is>
       </c>
       <c r="N287" s="6" t="n">
-        <v>22.9931513860828</v>
+        <v>24.8915014056924</v>
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
@@ -22559,7 +22755,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22596,7 +22792,7 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H288" s="4" t="inlineStr">
         <is>
@@ -22629,7 +22825,7 @@
         </is>
       </c>
       <c r="N288" s="6" t="n">
-        <v>16.1985343555775</v>
+        <v>22.9931513860828</v>
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
@@ -22638,7 +22834,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22675,7 +22871,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
@@ -22708,7 +22904,7 @@
         </is>
       </c>
       <c r="N289" s="6" t="n">
-        <v>15.8263995123574</v>
+        <v>16.1985343555775</v>
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
@@ -22717,7 +22913,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22754,7 +22950,7 @@
         </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
@@ -22787,7 +22983,7 @@
         </is>
       </c>
       <c r="N290" s="6" t="n">
-        <v>36.481380981255</v>
+        <v>15.8263995123574</v>
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
@@ -22796,7 +22992,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22833,7 +23029,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
@@ -22866,7 +23062,7 @@
         </is>
       </c>
       <c r="N291" s="6" t="n">
-        <v>34.4312946645093</v>
+        <v>36.481380981255</v>
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
@@ -22875,7 +23071,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22912,7 +23108,7 @@
         </is>
       </c>
       <c r="G292" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
@@ -22945,7 +23141,7 @@
         </is>
       </c>
       <c r="N292" s="6" t="n">
-        <v>24.750858904318</v>
+        <v>34.4312946645093</v>
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
@@ -22954,7 +23150,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -22991,7 +23187,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
@@ -23024,7 +23220,7 @@
         </is>
       </c>
       <c r="N293" s="6" t="n">
-        <v>13.1086608763643</v>
+        <v>24.750858904318</v>
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
@@ -23033,7 +23229,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23070,7 +23266,7 @@
         </is>
       </c>
       <c r="G294" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
@@ -23103,7 +23299,7 @@
         </is>
       </c>
       <c r="N294" s="6" t="n">
-        <v>17.0995109701258</v>
+        <v>13.1086608763643</v>
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
@@ -23112,7 +23308,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23149,7 +23345,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
@@ -23182,7 +23378,7 @@
         </is>
       </c>
       <c r="N295" s="6" t="n">
-        <v>19.0260300794035</v>
+        <v>17.0995109701258</v>
       </c>
       <c r="O295" s="4" t="inlineStr">
         <is>
@@ -23191,7 +23387,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23228,7 +23424,7 @@
         </is>
       </c>
       <c r="G296" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H296" s="4" t="inlineStr">
         <is>
@@ -23261,7 +23457,7 @@
         </is>
       </c>
       <c r="N296" s="6" t="n">
-        <v>16.3107385078032</v>
+        <v>19.0260300794035</v>
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
@@ -23270,7 +23466,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23307,7 +23503,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
@@ -23340,7 +23536,7 @@
         </is>
       </c>
       <c r="N297" s="6" t="n">
-        <v>8.00102414924425</v>
+        <v>16.3107385078032</v>
       </c>
       <c r="O297" s="4" t="inlineStr">
         <is>
@@ -23349,7 +23545,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23386,7 +23582,7 @@
         </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
@@ -23419,7 +23615,7 @@
         </is>
       </c>
       <c r="N298" s="6" t="n">
-        <v>15.9166311155573</v>
+        <v>8.00102414924425</v>
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
@@ -23428,7 +23624,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23465,7 +23661,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
@@ -23498,7 +23694,7 @@
         </is>
       </c>
       <c r="N299" s="6" t="n">
-        <v>10.0130859589153</v>
+        <v>15.9166311155573</v>
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
@@ -23507,7 +23703,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23544,7 +23740,7 @@
         </is>
       </c>
       <c r="G300" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
@@ -23577,7 +23773,7 @@
         </is>
       </c>
       <c r="N300" s="6" t="n">
-        <v>20.9626504331607</v>
+        <v>10.0130859589153</v>
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
@@ -23586,7 +23782,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23623,7 +23819,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
@@ -23656,7 +23852,7 @@
         </is>
       </c>
       <c r="N301" s="6" t="n">
-        <v>29.2548511239111</v>
+        <v>20.9626504331607</v>
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
@@ -23665,7 +23861,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23702,7 +23898,7 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
@@ -23735,7 +23931,7 @@
         </is>
       </c>
       <c r="N302" s="6" t="n">
-        <v>16.6639894189064</v>
+        <v>29.2548511239111</v>
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
@@ -23744,7 +23940,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23781,7 +23977,7 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
@@ -23814,7 +24010,7 @@
         </is>
       </c>
       <c r="N303" s="6" t="n">
-        <v>15.7571776112482</v>
+        <v>16.6639894189064</v>
       </c>
       <c r="O303" s="4" t="inlineStr">
         <is>
@@ -23823,7 +24019,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23860,7 +24056,7 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
@@ -23893,7 +24089,7 @@
         </is>
       </c>
       <c r="N304" s="6" t="n">
-        <v>15.7932181812518</v>
+        <v>15.7571776112482</v>
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
@@ -23902,7 +24098,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23939,7 +24135,7 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
@@ -23972,7 +24168,7 @@
         </is>
       </c>
       <c r="N305" s="6" t="n">
-        <v>16.2198265911409</v>
+        <v>15.7932181812518</v>
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
@@ -23981,7 +24177,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24018,7 +24214,7 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
@@ -24051,7 +24247,7 @@
         </is>
       </c>
       <c r="N306" s="6" t="n">
-        <v>15.1363210095652</v>
+        <v>16.2198265911409</v>
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
@@ -24060,7 +24256,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24097,7 +24293,7 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
@@ -24130,7 +24326,7 @@
         </is>
       </c>
       <c r="N307" s="6" t="n">
-        <v>23.8367720643582</v>
+        <v>15.1363210095652</v>
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
@@ -24139,7 +24335,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24176,7 +24372,7 @@
         </is>
       </c>
       <c r="G308" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
@@ -24209,7 +24405,7 @@
         </is>
       </c>
       <c r="N308" s="6" t="n">
-        <v>18.0963540802062</v>
+        <v>23.8367720643582</v>
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
@@ -24218,7 +24414,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24255,7 +24451,7 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
@@ -24288,7 +24484,7 @@
         </is>
       </c>
       <c r="N309" s="6" t="n">
-        <v>9.06347009522954</v>
+        <v>18.0963540802062</v>
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
@@ -24297,7 +24493,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24334,7 +24530,7 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
@@ -24367,7 +24563,7 @@
         </is>
       </c>
       <c r="N310" s="6" t="n">
-        <v>13.269532614572</v>
+        <v>9.06347009522954</v>
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
@@ -24376,7 +24572,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24413,7 +24609,7 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H311" s="4" t="inlineStr">
         <is>
@@ -24446,7 +24642,7 @@
         </is>
       </c>
       <c r="N311" s="6" t="n">
-        <v>20.5761295010598</v>
+        <v>13.269532614572</v>
       </c>
       <c r="O311" s="4" t="inlineStr">
         <is>
@@ -24455,7 +24651,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24492,7 +24688,7 @@
         </is>
       </c>
       <c r="G312" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
@@ -24525,7 +24721,7 @@
         </is>
       </c>
       <c r="N312" s="6" t="n">
-        <v>15.3442903568827</v>
+        <v>20.5761295010598</v>
       </c>
       <c r="O312" s="4" t="inlineStr">
         <is>
@@ -24534,7 +24730,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24767,7 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
@@ -24604,7 +24800,7 @@
         </is>
       </c>
       <c r="N313" s="6" t="n">
-        <v>19.4545884689745</v>
+        <v>15.3442903568827</v>
       </c>
       <c r="O313" s="4" t="inlineStr">
         <is>
@@ -24613,7 +24809,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24650,7 +24846,7 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
@@ -24683,7 +24879,7 @@
         </is>
       </c>
       <c r="N314" s="6" t="n">
-        <v>21.8955843439596</v>
+        <v>19.4545884689745</v>
       </c>
       <c r="O314" s="4" t="inlineStr">
         <is>
@@ -24692,7 +24888,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24729,7 +24925,7 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H315" s="4" t="inlineStr">
         <is>
@@ -24762,7 +24958,7 @@
         </is>
       </c>
       <c r="N315" s="6" t="n">
-        <v>23.8297115705399</v>
+        <v>21.8955843439596</v>
       </c>
       <c r="O315" s="4" t="inlineStr">
         <is>
@@ -24771,7 +24967,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +25004,7 @@
         </is>
       </c>
       <c r="G316" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H316" s="4" t="inlineStr">
         <is>
@@ -24841,7 +25037,7 @@
         </is>
       </c>
       <c r="N316" s="6" t="n">
-        <v>29.2230041014033</v>
+        <v>23.8297115705399</v>
       </c>
       <c r="O316" s="4" t="inlineStr">
         <is>
@@ -24850,7 +25046,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +25083,7 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
@@ -24920,7 +25116,7 @@
         </is>
       </c>
       <c r="N317" s="6" t="n">
-        <v>28.0774680117788</v>
+        <v>29.2230041014033</v>
       </c>
       <c r="O317" s="4" t="inlineStr">
         <is>
@@ -24929,7 +25125,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +25162,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
@@ -24999,7 +25195,7 @@
         </is>
       </c>
       <c r="N318" s="6" t="n">
-        <v>23.1186941835454</v>
+        <v>28.0774680117788</v>
       </c>
       <c r="O318" s="4" t="inlineStr">
         <is>
@@ -25008,7 +25204,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25045,7 +25241,7 @@
         </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H319" s="4" t="inlineStr">
         <is>
@@ -25078,7 +25274,7 @@
         </is>
       </c>
       <c r="N319" s="6" t="n">
-        <v>23.9223070628002</v>
+        <v>23.1186941835454</v>
       </c>
       <c r="O319" s="4" t="inlineStr">
         <is>
@@ -25087,7 +25283,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25124,7 +25320,7 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H320" s="4" t="inlineStr">
         <is>
@@ -25157,7 +25353,7 @@
         </is>
       </c>
       <c r="N320" s="6" t="n">
-        <v>10.5416668243022</v>
+        <v>23.9223070628002</v>
       </c>
       <c r="O320" s="4" t="inlineStr">
         <is>
@@ -25166,7 +25362,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25203,7 +25399,7 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H321" s="4" t="inlineStr">
         <is>
@@ -25236,7 +25432,7 @@
         </is>
       </c>
       <c r="N321" s="6" t="n">
-        <v>12.380878328857</v>
+        <v>10.5416668243022</v>
       </c>
       <c r="O321" s="4" t="inlineStr">
         <is>
@@ -25245,7 +25441,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25282,7 +25478,7 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H322" s="4" t="inlineStr">
         <is>
@@ -25315,7 +25511,7 @@
         </is>
       </c>
       <c r="N322" s="6" t="n">
-        <v>24.4753357613612</v>
+        <v>12.380878328857</v>
       </c>
       <c r="O322" s="4" t="inlineStr">
         <is>
@@ -25324,7 +25520,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25557,7 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
@@ -25394,7 +25590,7 @@
         </is>
       </c>
       <c r="N323" s="6" t="n">
-        <v>18.7812359044725</v>
+        <v>24.4753357613612</v>
       </c>
       <c r="O323" s="4" t="inlineStr">
         <is>
@@ -25403,7 +25599,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25440,7 +25636,7 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H324" s="4" t="inlineStr">
         <is>
@@ -25473,7 +25669,7 @@
         </is>
       </c>
       <c r="N324" s="6" t="n">
-        <v>17.6253449138361</v>
+        <v>18.7812359044725</v>
       </c>
       <c r="O324" s="4" t="inlineStr">
         <is>
@@ -25482,7 +25678,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25519,7 +25715,7 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
@@ -25552,7 +25748,7 @@
         </is>
       </c>
       <c r="N325" s="6" t="n">
-        <v>11.8465082797294</v>
+        <v>17.6253449138361</v>
       </c>
       <c r="O325" s="4" t="inlineStr">
         <is>
@@ -25561,7 +25757,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25598,7 +25794,7 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
@@ -25630,7 +25826,9 @@
           <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N326" s="4" t="n"/>
+      <c r="N326" s="6" t="n">
+        <v>11.8465082797294</v>
+      </c>
       <c r="O326" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -25638,7 +25836,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25675,7 +25873,7 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H327" s="4" t="inlineStr">
         <is>
@@ -25715,7 +25913,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25752,7 +25950,7 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H328" s="4" t="inlineStr">
         <is>
@@ -25792,7 +25990,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25829,7 +26027,7 @@
         </is>
       </c>
       <c r="G329" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H329" s="4" t="inlineStr">
         <is>
@@ -25869,7 +26067,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25906,7 +26104,7 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H330" s="4" t="inlineStr">
         <is>
@@ -25946,7 +26144,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25983,7 +26181,7 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
@@ -26023,7 +26221,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26060,7 +26258,7 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H332" s="4" t="inlineStr">
         <is>
@@ -26100,7 +26298,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26137,7 +26335,7 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
@@ -26177,7 +26375,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26214,7 +26412,7 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H334" s="4" t="inlineStr">
         <is>
@@ -26254,7 +26452,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26291,7 +26489,7 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
@@ -26331,7 +26529,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26368,7 +26566,7 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H336" s="4" t="inlineStr">
         <is>
@@ -26408,10 +26606,87 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H337" s="4" t="inlineStr">
+        <is>
+          <t>Energía y ambiente</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>energia_y_ambiente</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr">
+        <is>
+          <t>Recursos naturales</t>
+        </is>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>recursos_naturales</t>
+        </is>
+      </c>
+      <c r="L337" s="4" t="inlineStr">
+        <is>
+          <t>NY.GDP.TOTL.RT.ZS</t>
+        </is>
+      </c>
+      <c r="M337" s="4" t="inlineStr">
+        <is>
+          <t>Rentas totales de recursos naturales como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="N337" s="4" t="n"/>
+      <c r="O337" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P337" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="Q337" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26493,7 +26768,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -26514,7 +26789,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
